--- a/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
+++ b/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\project\unity\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AAD5D9-ED00-485D-A4E3-209D176361AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF1EBBF-09EF-4872-80D8-178520BCEDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{85F091D7-8DEA-4479-A83C-808C693C032A}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="459">
   <si>
     <t>名字</t>
   </si>
@@ -211,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprite/SkillIcon/Icon_Magic1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>持续时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -727,9 +723,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sprite/SkillIcon/Icon_Magic0</t>
-  </si>
-  <si>
     <t>MAW Mortar Napalm Bomb Lvl.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1739,6 +1732,10 @@
   </si>
   <si>
     <t>AssaultMech Shoot F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill/Icon_Magic1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2121,22 +2118,22 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K1" t="s">
         <v>42</v>
@@ -2148,7 +2145,7 @@
         <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O1" t="s">
         <v>2</v>
@@ -2172,10 +2169,10 @@
         <v>39</v>
       </c>
       <c r="V1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="X1" t="s">
         <v>14</v>
@@ -2187,7 +2184,7 @@
         <v>34</v>
       </c>
       <c r="AA1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AB1" t="s">
         <v>16</v>
@@ -2210,28 +2207,28 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
         <v>115</v>
       </c>
-      <c r="F2" t="s">
-        <v>116</v>
-      </c>
       <c r="G2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="J2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K2" t="s">
         <v>45</v>
@@ -2243,7 +2240,7 @@
         <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="O2" t="s">
         <v>4</v>
@@ -2267,10 +2264,10 @@
         <v>40</v>
       </c>
       <c r="V2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="W2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="X2" t="s">
         <v>22</v>
@@ -2282,7 +2279,7 @@
         <v>33</v>
       </c>
       <c r="AA2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AB2" t="s">
         <v>15</v>
@@ -2306,10 +2303,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -2357,10 +2354,10 @@
         <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="W3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="X3" t="s">
         <v>21</v>
@@ -2387,13 +2384,13 @@
         <v>5</v>
       </c>
       <c r="AH3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AJ3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
@@ -2401,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2456,11 +2453,11 @@
         <v>31</v>
       </c>
       <c r="U4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z4" t="s">
         <v>51</v>
       </c>
-      <c r="Z4" t="s">
-        <v>52</v>
-      </c>
       <c r="AA4" t="b">
         <v>1</v>
       </c>
@@ -2471,16 +2468,16 @@
         <v>1</v>
       </c>
       <c r="AE4" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AH4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AI4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AJ4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -2488,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2543,10 +2540,10 @@
         <v>31</v>
       </c>
       <c r="U5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -2558,16 +2555,16 @@
         <v>1</v>
       </c>
       <c r="AE5" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AH5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AI5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AJ5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
@@ -2575,7 +2572,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2630,10 +2627,10 @@
         <v>31</v>
       </c>
       <c r="U6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -2645,13 +2642,13 @@
         <v>1</v>
       </c>
       <c r="AE6" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AI6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AJ6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
@@ -2659,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2714,10 +2711,10 @@
         <v>31</v>
       </c>
       <c r="U7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA7" t="b">
         <v>1</v>
@@ -2729,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="AE7" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AJ7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -2740,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2795,10 +2792,10 @@
         <v>31</v>
       </c>
       <c r="U8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Z8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -2810,10 +2807,10 @@
         <v>1</v>
       </c>
       <c r="AE8" t="s">
-        <v>191</v>
+        <v>458</v>
       </c>
       <c r="AJ8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
@@ -2821,7 +2818,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2876,10 +2873,10 @@
         <v>31</v>
       </c>
       <c r="U9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -2891,10 +2888,10 @@
         <v>1</v>
       </c>
       <c r="AE9" t="s">
-        <v>191</v>
+        <v>458</v>
       </c>
       <c r="AJ9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
@@ -2902,7 +2899,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2957,7 +2954,7 @@
         <v>31</v>
       </c>
       <c r="U10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA10" t="b">
         <v>1</v>
@@ -2969,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="AE10" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AJ10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
@@ -2980,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -3035,7 +3032,7 @@
         <v>31</v>
       </c>
       <c r="U11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -3047,10 +3044,10 @@
         <v>1</v>
       </c>
       <c r="AE11" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AJ11" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
@@ -3058,7 +3055,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -3113,7 +3110,7 @@
         <v>31</v>
       </c>
       <c r="U12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -3125,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="AE12" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
       <c r="AJ12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.2">
@@ -3136,7 +3133,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -3191,7 +3188,7 @@
         <v>31</v>
       </c>
       <c r="U13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -3203,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
@@ -3211,7 +3208,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -3266,10 +3263,10 @@
         <v>31</v>
       </c>
       <c r="U14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="W14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -3281,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
@@ -3289,7 +3286,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -3344,7 +3341,7 @@
         <v>31</v>
       </c>
       <c r="U15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -3356,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="AE15" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
@@ -3364,7 +3361,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -3419,10 +3416,10 @@
         <v>31</v>
       </c>
       <c r="U16" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Z16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -3434,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="AE16" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.2">
@@ -3442,7 +3439,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -3497,10 +3494,10 @@
         <v>31</v>
       </c>
       <c r="U17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -3512,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="AE17" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.2">
@@ -3520,7 +3517,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C18">
         <v>7</v>
@@ -3575,10 +3572,10 @@
         <v>31</v>
       </c>
       <c r="U18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3590,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="AE18" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.2">
@@ -3598,7 +3595,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -3653,10 +3650,10 @@
         <v>31</v>
       </c>
       <c r="U19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="W19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3668,7 +3665,7 @@
         <v>1</v>
       </c>
       <c r="AE19" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.2">
@@ -3676,7 +3673,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C20">
         <v>9</v>
@@ -3731,10 +3728,10 @@
         <v>31</v>
       </c>
       <c r="U20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Z20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3746,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="AE20" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.2">
@@ -3754,7 +3751,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -3809,10 +3806,10 @@
         <v>31</v>
       </c>
       <c r="U21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Z21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -3824,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="AE21" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
@@ -3832,7 +3829,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -3887,10 +3884,10 @@
         <v>31</v>
       </c>
       <c r="U22" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="Z22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -3902,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.2">
@@ -3910,7 +3907,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -3965,16 +3962,16 @@
         <v>31</v>
       </c>
       <c r="U23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="V23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="W23" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -3986,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="AE23" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
@@ -3994,7 +3991,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -4049,16 +4046,16 @@
         <v>31</v>
       </c>
       <c r="U24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="W24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -4070,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="AE24" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:31" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4078,7 +4075,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -4133,16 +4130,16 @@
         <v>31</v>
       </c>
       <c r="U25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="W25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA25" t="b">
         <v>1</v>
@@ -4154,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="AE25" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
@@ -4162,7 +4159,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C26">
         <v>11</v>
@@ -4217,10 +4214,10 @@
         <v>31</v>
       </c>
       <c r="U26" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="b">
         <v>1</v>
@@ -4232,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="AE26" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.2">
@@ -4240,7 +4237,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C27">
         <v>11</v>
@@ -4295,10 +4292,10 @@
         <v>31</v>
       </c>
       <c r="U27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="Z27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4310,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="AE27" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.2">
@@ -4318,7 +4315,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C28">
         <v>11</v>
@@ -4373,10 +4370,10 @@
         <v>31</v>
       </c>
       <c r="U28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Z28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -4388,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="AE28" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.2">
@@ -4396,7 +4393,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -4451,10 +4448,10 @@
         <v>31</v>
       </c>
       <c r="U29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="b">
         <v>1</v>
@@ -4466,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="AE29" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.2">
@@ -4474,7 +4471,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -4529,10 +4526,10 @@
         <v>31</v>
       </c>
       <c r="U30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA30" t="b">
         <v>1</v>
@@ -4544,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.2">
@@ -4552,7 +4549,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -4607,10 +4604,10 @@
         <v>31</v>
       </c>
       <c r="U31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4622,7 +4619,7 @@
         <v>1</v>
       </c>
       <c r="AE31" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.2">
@@ -4630,7 +4627,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -4685,10 +4682,10 @@
         <v>31</v>
       </c>
       <c r="U32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Z32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="b">
         <v>1</v>
@@ -4700,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="AE32" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.2">
@@ -4708,7 +4705,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C33">
         <v>12</v>
@@ -4763,10 +4760,10 @@
         <v>31</v>
       </c>
       <c r="U33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -4778,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="AE33" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.2">
@@ -4786,7 +4783,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C34">
         <v>13</v>
@@ -4841,10 +4838,10 @@
         <v>31</v>
       </c>
       <c r="U34" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Z34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA34" t="b">
         <v>1</v>
@@ -4856,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="AE34" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.2">
@@ -4864,7 +4861,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C35">
         <v>13</v>
@@ -4919,10 +4916,10 @@
         <v>31</v>
       </c>
       <c r="U35" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="Z35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA35" t="b">
         <v>1</v>
@@ -4934,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="AE35" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.2">
@@ -4942,7 +4939,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C36">
         <v>13</v>
@@ -4997,10 +4994,10 @@
         <v>31</v>
       </c>
       <c r="U36" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="Z36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA36" t="b">
         <v>1</v>
@@ -5012,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="AE36" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
@@ -5020,7 +5017,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C37">
         <v>14</v>
@@ -5075,7 +5072,7 @@
         <v>31</v>
       </c>
       <c r="U37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA37" t="b">
         <v>1</v>
@@ -5087,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="AE37" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
@@ -5095,7 +5092,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C38">
         <v>14</v>
@@ -5150,7 +5147,7 @@
         <v>31</v>
       </c>
       <c r="U38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -5162,7 +5159,7 @@
         <v>1</v>
       </c>
       <c r="AE38" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.2">
@@ -5170,7 +5167,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C39">
         <v>14</v>
@@ -5225,7 +5222,7 @@
         <v>31</v>
       </c>
       <c r="U39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AA39" t="b">
         <v>1</v>
@@ -5237,7 +5234,7 @@
         <v>1</v>
       </c>
       <c r="AE39" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.2">
@@ -5245,7 +5242,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C40">
         <v>15</v>
@@ -5300,7 +5297,7 @@
         <v>31</v>
       </c>
       <c r="U40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA40" t="b">
         <v>1</v>
@@ -5312,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="AE40" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
@@ -5320,7 +5317,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C41">
         <v>15</v>
@@ -5375,7 +5372,7 @@
         <v>31</v>
       </c>
       <c r="U41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA41" t="b">
         <v>1</v>
@@ -5387,7 +5384,7 @@
         <v>1</v>
       </c>
       <c r="AE41" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
@@ -5395,7 +5392,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C42">
         <v>15</v>
@@ -5450,7 +5447,7 @@
         <v>31</v>
       </c>
       <c r="U42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AA42" t="b">
         <v>1</v>
@@ -5462,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="AE42" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
@@ -5470,7 +5467,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C43">
         <v>16</v>
@@ -5525,7 +5522,7 @@
         <v>31</v>
       </c>
       <c r="U43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -5537,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="AE43" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
@@ -5545,7 +5542,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C44">
         <v>16</v>
@@ -5600,7 +5597,7 @@
         <v>31</v>
       </c>
       <c r="U44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
@@ -5612,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="AE44" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.2">
@@ -5620,7 +5617,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C45">
         <v>16</v>
@@ -5675,7 +5672,7 @@
         <v>31</v>
       </c>
       <c r="U45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
@@ -5687,7 +5684,7 @@
         <v>1</v>
       </c>
       <c r="AE45" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
@@ -5695,7 +5692,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C46">
         <v>16</v>
@@ -5750,7 +5747,7 @@
         <v>31</v>
       </c>
       <c r="U46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
@@ -5762,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="AE46" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
@@ -5770,7 +5767,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C47">
         <v>16</v>
@@ -5825,7 +5822,7 @@
         <v>31</v>
       </c>
       <c r="U47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
@@ -5837,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="AE47" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
@@ -5845,7 +5842,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C48">
         <v>17</v>
@@ -5900,7 +5897,7 @@
         <v>31</v>
       </c>
       <c r="U48" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
@@ -5912,7 +5909,7 @@
         <v>1</v>
       </c>
       <c r="AE48" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.2">
@@ -5920,7 +5917,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C49">
         <v>17</v>
@@ -5975,7 +5972,7 @@
         <v>31</v>
       </c>
       <c r="U49" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
@@ -5987,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="AE49" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.2">
@@ -5995,7 +5992,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C50">
         <v>17</v>
@@ -6050,7 +6047,7 @@
         <v>31</v>
       </c>
       <c r="U50" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
@@ -6062,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="AE50" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.2">
@@ -6070,7 +6067,7 @@
         <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C51">
         <v>17</v>
@@ -6125,7 +6122,7 @@
         <v>31</v>
       </c>
       <c r="U51" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
@@ -6137,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="AE51" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.2">
@@ -6145,7 +6142,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C52">
         <v>17</v>
@@ -6200,7 +6197,7 @@
         <v>31</v>
       </c>
       <c r="U52" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AA52" t="b">
         <v>1</v>
@@ -6212,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="AE52" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.2">
@@ -6220,7 +6217,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C53">
         <v>9</v>
@@ -6275,7 +6272,7 @@
         <v>31</v>
       </c>
       <c r="U53" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AA53" t="b">
         <v>1</v>
@@ -6287,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="AE53" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.2">
@@ -6295,7 +6292,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C54">
         <v>9</v>
@@ -6350,7 +6347,7 @@
         <v>31</v>
       </c>
       <c r="U54" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AA54" t="b">
         <v>1</v>
@@ -6362,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="AE54" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.2">
@@ -6370,7 +6367,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C55">
         <v>18</v>
@@ -6425,10 +6422,10 @@
         <v>31</v>
       </c>
       <c r="U55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="W55" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AA55" t="b">
         <v>1</v>
@@ -6440,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="AE55" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
@@ -6448,7 +6445,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C56">
         <v>18</v>
@@ -6503,10 +6500,10 @@
         <v>31</v>
       </c>
       <c r="U56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="W56" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AA56" t="b">
         <v>1</v>
@@ -6518,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="AE56" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.2">
@@ -6526,7 +6523,7 @@
         <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C57">
         <v>18</v>
@@ -6581,10 +6578,10 @@
         <v>31</v>
       </c>
       <c r="U57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W57" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AA57" t="b">
         <v>1</v>
@@ -6596,7 +6593,7 @@
         <v>1</v>
       </c>
       <c r="AE57" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.2">
@@ -6604,7 +6601,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C58">
         <v>18</v>
@@ -6659,7 +6656,7 @@
         <v>31</v>
       </c>
       <c r="U58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AA58" t="b">
         <v>1</v>
@@ -6671,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="AE58" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" spans="1:31" x14ac:dyDescent="0.2">
@@ -6679,7 +6676,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C59">
         <v>18</v>
@@ -6734,7 +6731,7 @@
         <v>31</v>
       </c>
       <c r="U59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AA59" t="b">
         <v>1</v>
@@ -6746,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="AE59" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="60" spans="1:31" x14ac:dyDescent="0.2">
@@ -6754,7 +6751,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C60">
         <v>19</v>
@@ -6809,16 +6806,16 @@
         <v>31</v>
       </c>
       <c r="U60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W60" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA60" t="b">
         <v>1</v>
@@ -6830,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="AE60" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61" spans="1:31" x14ac:dyDescent="0.2">
@@ -6838,7 +6835,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C61">
         <v>19</v>
@@ -6893,16 +6890,16 @@
         <v>31</v>
       </c>
       <c r="U61" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V61" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA61" t="b">
         <v>1</v>
@@ -6914,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="AE61" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="1:31" x14ac:dyDescent="0.2">
@@ -6922,7 +6919,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C62">
         <v>19</v>
@@ -6977,16 +6974,16 @@
         <v>31</v>
       </c>
       <c r="U62" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="V62" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W62" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Z62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AA62" t="b">
         <v>1</v>
@@ -6998,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="AE62" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="63" spans="1:31" x14ac:dyDescent="0.2">
@@ -7028,7 +7025,7 @@
         <v>80</v>
       </c>
       <c r="B65" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C65">
         <v>20</v>
@@ -7067,13 +7064,13 @@
         <v>0</v>
       </c>
       <c r="R65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S65" t="s">
         <v>32</v>
       </c>
       <c r="T65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X65">
         <v>180</v>
@@ -7088,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.2">
@@ -7096,7 +7093,7 @@
         <v>81</v>
       </c>
       <c r="B66" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C66">
         <v>20</v>
@@ -7135,13 +7132,13 @@
         <v>0</v>
       </c>
       <c r="R66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S66" t="s">
         <v>32</v>
       </c>
       <c r="T66" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X66">
         <v>181</v>
@@ -7156,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="AE66" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="67" spans="1:31" x14ac:dyDescent="0.2">
@@ -7164,7 +7161,7 @@
         <v>82</v>
       </c>
       <c r="B67" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C67">
         <v>20</v>
@@ -7203,13 +7200,13 @@
         <v>0</v>
       </c>
       <c r="R67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S67" t="s">
         <v>32</v>
       </c>
       <c r="T67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X67">
         <v>182</v>
@@ -7224,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="AE67" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.2">
@@ -7232,7 +7229,7 @@
         <v>83</v>
       </c>
       <c r="B68" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C68">
         <v>21</v>
@@ -7271,13 +7268,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S68" t="s">
         <v>32</v>
       </c>
       <c r="T68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X68">
         <v>183</v>
@@ -7292,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="AE68" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="1:31" x14ac:dyDescent="0.2">
@@ -7300,7 +7297,7 @@
         <v>84</v>
       </c>
       <c r="B69" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C69">
         <v>21</v>
@@ -7339,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S69" t="s">
         <v>32</v>
       </c>
       <c r="T69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X69">
         <v>184</v>
@@ -7360,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="AE69" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:31" x14ac:dyDescent="0.2">
@@ -7368,7 +7365,7 @@
         <v>85</v>
       </c>
       <c r="B70" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C70">
         <v>21</v>
@@ -7407,13 +7404,13 @@
         <v>0</v>
       </c>
       <c r="R70" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S70" t="s">
         <v>32</v>
       </c>
       <c r="T70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X70">
         <v>185</v>
@@ -7428,7 +7425,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="71" spans="1:31" x14ac:dyDescent="0.2">
@@ -7436,7 +7433,7 @@
         <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C71">
         <v>22</v>
@@ -7475,13 +7472,13 @@
         <v>0</v>
       </c>
       <c r="R71" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S71" t="s">
         <v>32</v>
       </c>
       <c r="T71" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X71">
         <v>186</v>
@@ -7496,7 +7493,7 @@
         <v>0</v>
       </c>
       <c r="AE71" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.2">
@@ -7504,7 +7501,7 @@
         <v>87</v>
       </c>
       <c r="B72" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C72">
         <v>22</v>
@@ -7543,13 +7540,13 @@
         <v>0</v>
       </c>
       <c r="R72" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S72" t="s">
         <v>32</v>
       </c>
       <c r="T72" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X72">
         <v>187</v>
@@ -7564,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="AE72" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="73" spans="1:31" x14ac:dyDescent="0.2">
@@ -7572,7 +7569,7 @@
         <v>88</v>
       </c>
       <c r="B73" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C73">
         <v>22</v>
@@ -7611,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S73" t="s">
         <v>32</v>
       </c>
       <c r="T73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X73">
         <v>188</v>
@@ -7632,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="AE73" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.2">
@@ -7640,7 +7637,7 @@
         <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C74">
         <v>23</v>
@@ -7679,13 +7676,13 @@
         <v>0</v>
       </c>
       <c r="R74" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S74" t="s">
         <v>32</v>
       </c>
       <c r="T74" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X74">
         <v>189</v>
@@ -7700,7 +7697,7 @@
         <v>0</v>
       </c>
       <c r="AE74" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="75" spans="1:31" x14ac:dyDescent="0.2">
@@ -7708,7 +7705,7 @@
         <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C75">
         <v>23</v>
@@ -7747,13 +7744,13 @@
         <v>0</v>
       </c>
       <c r="R75" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S75" t="s">
         <v>32</v>
       </c>
       <c r="T75" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X75">
         <v>190</v>
@@ -7768,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="AE75" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
@@ -7776,7 +7773,7 @@
         <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C76">
         <v>23</v>
@@ -7815,13 +7812,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S76" t="s">
         <v>32</v>
       </c>
       <c r="T76" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X76">
         <v>191</v>
@@ -7836,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="AE76" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="77" spans="1:31" x14ac:dyDescent="0.2">
@@ -7844,7 +7841,7 @@
         <v>92</v>
       </c>
       <c r="B77" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C77">
         <v>24</v>
@@ -7883,13 +7880,13 @@
         <v>3</v>
       </c>
       <c r="R77" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S77" t="s">
         <v>32</v>
       </c>
       <c r="T77" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X77">
         <v>192</v>
@@ -7904,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
@@ -7912,7 +7909,7 @@
         <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C78">
         <v>24</v>
@@ -7951,13 +7948,13 @@
         <v>3</v>
       </c>
       <c r="R78" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S78" t="s">
         <v>32</v>
       </c>
       <c r="T78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X78">
         <v>193</v>
@@ -7972,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
@@ -7980,7 +7977,7 @@
         <v>94</v>
       </c>
       <c r="B79" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C79">
         <v>24</v>
@@ -8019,13 +8016,13 @@
         <v>3</v>
       </c>
       <c r="R79" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S79" t="s">
         <v>32</v>
       </c>
       <c r="T79" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X79">
         <v>194</v>
@@ -8040,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
@@ -8048,7 +8045,7 @@
         <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C80">
         <v>25</v>
@@ -8087,13 +8084,13 @@
         <v>3</v>
       </c>
       <c r="R80" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S80" t="s">
         <v>32</v>
       </c>
       <c r="T80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X80">
         <v>195</v>
@@ -8108,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="81" spans="1:31" x14ac:dyDescent="0.2">
@@ -8116,7 +8113,7 @@
         <v>96</v>
       </c>
       <c r="B81" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C81">
         <v>25</v>
@@ -8155,13 +8152,13 @@
         <v>3</v>
       </c>
       <c r="R81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S81" t="s">
         <v>32</v>
       </c>
       <c r="T81" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X81">
         <v>196</v>
@@ -8176,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AE81" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="82" spans="1:31" x14ac:dyDescent="0.2">
@@ -8184,7 +8181,7 @@
         <v>97</v>
       </c>
       <c r="B82" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C82">
         <v>25</v>
@@ -8223,13 +8220,13 @@
         <v>3</v>
       </c>
       <c r="R82" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S82" t="s">
         <v>32</v>
       </c>
       <c r="T82" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X82">
         <v>197</v>
@@ -8244,7 +8241,7 @@
         <v>0</v>
       </c>
       <c r="AE82" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="83" spans="1:31" x14ac:dyDescent="0.2">
@@ -8252,7 +8249,7 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C83">
         <v>26</v>
@@ -8291,13 +8288,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S83" t="s">
         <v>32</v>
       </c>
       <c r="T83" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X83">
         <v>198</v>
@@ -8312,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="84" spans="1:31" x14ac:dyDescent="0.2">
@@ -8320,7 +8317,7 @@
         <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C84">
         <v>26</v>
@@ -8359,13 +8356,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S84" t="s">
         <v>32</v>
       </c>
       <c r="T84" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X84">
         <v>199</v>
@@ -8380,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="AE84" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:31" x14ac:dyDescent="0.2">
@@ -8388,7 +8385,7 @@
         <v>100</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C85">
         <v>26</v>
@@ -8427,13 +8424,13 @@
         <v>0</v>
       </c>
       <c r="R85" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S85" t="s">
         <v>32</v>
       </c>
       <c r="T85" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X85">
         <v>200</v>
@@ -8448,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="86" spans="1:31" x14ac:dyDescent="0.2">
@@ -8456,7 +8453,7 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C86">
         <v>27</v>
@@ -8495,13 +8492,13 @@
         <v>0</v>
       </c>
       <c r="R86" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S86" t="s">
         <v>32</v>
       </c>
       <c r="T86" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X86">
         <v>201</v>
@@ -8516,7 +8513,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" spans="1:31" x14ac:dyDescent="0.2">
@@ -8524,7 +8521,7 @@
         <v>102</v>
       </c>
       <c r="B87" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C87">
         <v>27</v>
@@ -8563,13 +8560,13 @@
         <v>0</v>
       </c>
       <c r="R87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S87" t="s">
         <v>32</v>
       </c>
       <c r="T87" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X87">
         <v>202</v>
@@ -8584,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="88" spans="1:31" x14ac:dyDescent="0.2">
@@ -8592,7 +8589,7 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C88">
         <v>27</v>
@@ -8631,13 +8628,13 @@
         <v>0</v>
       </c>
       <c r="R88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S88" t="s">
         <v>32</v>
       </c>
       <c r="T88" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X88">
         <v>203</v>
@@ -8652,7 +8649,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="89" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -8660,7 +8657,7 @@
         <v>104</v>
       </c>
       <c r="B89" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C89">
         <v>28</v>
@@ -8699,16 +8696,16 @@
         <v>0</v>
       </c>
       <c r="R89" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S89" t="s">
         <v>32</v>
       </c>
       <c r="T89" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -8720,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="AE89" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="90" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -8728,7 +8725,7 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C90">
         <v>28</v>
@@ -8767,16 +8764,16 @@
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S90" t="s">
         <v>32</v>
       </c>
       <c r="T90" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -8788,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="AE90" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="91" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -8796,7 +8793,7 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C91">
         <v>28</v>
@@ -8835,16 +8832,16 @@
         <v>0</v>
       </c>
       <c r="R91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S91" t="s">
         <v>32</v>
       </c>
       <c r="T91" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -8856,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="AE91" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -8864,7 +8861,7 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C92">
         <v>29</v>
@@ -8903,16 +8900,16 @@
         <v>0</v>
       </c>
       <c r="R92" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S92" t="s">
         <v>32</v>
       </c>
       <c r="T92" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -8924,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="AE92" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="93" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -8932,7 +8929,7 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C93">
         <v>29</v>
@@ -8971,16 +8968,16 @@
         <v>0</v>
       </c>
       <c r="R93" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S93" t="s">
         <v>32</v>
       </c>
       <c r="T93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -8992,7 +8989,7 @@
         <v>1</v>
       </c>
       <c r="AE93" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9000,7 +8997,7 @@
         <v>109</v>
       </c>
       <c r="B94" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C94">
         <v>29</v>
@@ -9039,16 +9036,16 @@
         <v>0</v>
       </c>
       <c r="R94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S94" t="s">
         <v>32</v>
       </c>
       <c r="T94" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -9060,7 +9057,7 @@
         <v>1</v>
       </c>
       <c r="AE94" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="95" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9068,7 +9065,7 @@
         <v>110</v>
       </c>
       <c r="B95" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C95">
         <v>30</v>
@@ -9107,7 +9104,7 @@
         <v>2</v>
       </c>
       <c r="R95" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S95" t="s">
         <v>32</v>
@@ -9116,10 +9113,10 @@
         <v>31</v>
       </c>
       <c r="U95" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -9131,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="AE95" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="96" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9139,7 +9136,7 @@
         <v>111</v>
       </c>
       <c r="B96" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C96">
         <v>30</v>
@@ -9178,7 +9175,7 @@
         <v>2</v>
       </c>
       <c r="R96" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S96" t="s">
         <v>32</v>
@@ -9187,10 +9184,10 @@
         <v>31</v>
       </c>
       <c r="U96" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -9202,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="AE96" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="97" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9210,7 +9207,7 @@
         <v>112</v>
       </c>
       <c r="B97" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C97">
         <v>30</v>
@@ -9249,7 +9246,7 @@
         <v>2</v>
       </c>
       <c r="R97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S97" t="s">
         <v>32</v>
@@ -9258,10 +9255,10 @@
         <v>31</v>
       </c>
       <c r="U97" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -9273,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="AE97" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="98" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9281,7 +9278,7 @@
         <v>113</v>
       </c>
       <c r="B98" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C98">
         <v>31</v>
@@ -9320,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="R98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S98" t="s">
         <v>32</v>
@@ -9329,7 +9326,7 @@
         <v>31</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="X98">
         <v>204</v>
@@ -9344,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="AE98" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="99" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9352,7 +9349,7 @@
         <v>114</v>
       </c>
       <c r="B99" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C99">
         <v>31</v>
@@ -9391,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="R99" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S99" t="s">
         <v>32</v>
@@ -9400,7 +9397,7 @@
         <v>31</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="X99">
         <v>205</v>
@@ -9415,7 +9412,7 @@
         <v>1</v>
       </c>
       <c r="AE99" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="100" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9423,7 +9420,7 @@
         <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C100">
         <v>31</v>
@@ -9462,7 +9459,7 @@
         <v>1</v>
       </c>
       <c r="R100" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S100" t="s">
         <v>32</v>
@@ -9471,7 +9468,7 @@
         <v>31</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="X100">
         <v>206</v>
@@ -9486,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="AE100" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="101" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9494,7 +9491,7 @@
         <v>116</v>
       </c>
       <c r="B101" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C101">
         <v>32</v>
@@ -9533,7 +9530,7 @@
         <v>1</v>
       </c>
       <c r="R101" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S101" t="s">
         <v>32</v>
@@ -9542,10 +9539,10 @@
         <v>31</v>
       </c>
       <c r="U101" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -9557,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="AE101" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="102" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9565,7 +9562,7 @@
         <v>117</v>
       </c>
       <c r="B102" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C102">
         <v>32</v>
@@ -9604,7 +9601,7 @@
         <v>1</v>
       </c>
       <c r="R102" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S102" t="s">
         <v>32</v>
@@ -9613,10 +9610,10 @@
         <v>31</v>
       </c>
       <c r="U102" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -9628,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="AE102" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9636,7 +9633,7 @@
         <v>118</v>
       </c>
       <c r="B103" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C103">
         <v>32</v>
@@ -9675,7 +9672,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S103" t="s">
         <v>32</v>
@@ -9684,10 +9681,10 @@
         <v>31</v>
       </c>
       <c r="U103" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -9699,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="AE103" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="104" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9707,7 +9704,7 @@
         <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C104">
         <v>33</v>
@@ -9746,7 +9743,7 @@
         <v>2</v>
       </c>
       <c r="R104" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S104" t="s">
         <v>32</v>
@@ -9755,11 +9752,11 @@
         <v>31</v>
       </c>
       <c r="U104" t="s">
+        <v>286</v>
+      </c>
+      <c r="W104" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="W104" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="AA104" t="b">
         <v>0</v>
       </c>
@@ -9770,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="AE104" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="105" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9778,7 +9775,7 @@
         <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C105">
         <v>33</v>
@@ -9817,7 +9814,7 @@
         <v>2</v>
       </c>
       <c r="R105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S105" t="s">
         <v>32</v>
@@ -9826,10 +9823,10 @@
         <v>31</v>
       </c>
       <c r="U105" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -9841,7 +9838,7 @@
         <v>1</v>
       </c>
       <c r="AE105" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
@@ -9849,7 +9846,7 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C106">
         <v>33</v>
@@ -9888,7 +9885,7 @@
         <v>2</v>
       </c>
       <c r="R106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S106" t="s">
         <v>32</v>
@@ -9897,10 +9894,10 @@
         <v>31</v>
       </c>
       <c r="U106" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -9912,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="AE106" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="107" spans="1:31" x14ac:dyDescent="0.2">
@@ -9920,7 +9917,7 @@
         <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C107">
         <v>34</v>
@@ -9972,10 +9969,10 @@
         <v>31</v>
       </c>
       <c r="U107" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="W107" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -9987,7 +9984,7 @@
         <v>0</v>
       </c>
       <c r="AE107" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="108" spans="1:31" x14ac:dyDescent="0.2">
@@ -9995,7 +9992,7 @@
         <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C108">
         <v>34</v>
@@ -10047,10 +10044,10 @@
         <v>31</v>
       </c>
       <c r="U108" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="W108" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -10062,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="AE108" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="109" spans="1:31" x14ac:dyDescent="0.2">
@@ -10070,7 +10067,7 @@
         <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C109">
         <v>34</v>
@@ -10122,10 +10119,10 @@
         <v>31</v>
       </c>
       <c r="U109" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="W109" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -10137,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="AE109" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="110" spans="1:31" x14ac:dyDescent="0.2">
@@ -10145,7 +10142,7 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C110">
         <v>35</v>
@@ -10197,10 +10194,10 @@
         <v>31</v>
       </c>
       <c r="U110" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="Z110" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -10212,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AE110" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="111" spans="1:31" x14ac:dyDescent="0.2">
@@ -10220,7 +10217,7 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C111">
         <v>35</v>
@@ -10272,11 +10269,11 @@
         <v>31</v>
       </c>
       <c r="U111" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z111" t="s">
         <v>314</v>
       </c>
-      <c r="Z111" t="s">
-        <v>316</v>
-      </c>
       <c r="AA111" t="b">
         <v>0</v>
       </c>
@@ -10287,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="AE111" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="112" spans="1:31" x14ac:dyDescent="0.2">
@@ -10295,7 +10292,7 @@
         <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C112">
         <v>35</v>
@@ -10347,10 +10344,10 @@
         <v>31</v>
       </c>
       <c r="U112" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="Z112" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -10362,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="AE112" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="113" spans="1:31" x14ac:dyDescent="0.2">
@@ -10370,7 +10367,7 @@
         <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C113">
         <v>39</v>
@@ -10422,16 +10419,16 @@
         <v>31</v>
       </c>
       <c r="U113" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="W113" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="X113">
         <v>1</v>
       </c>
       <c r="Z113" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA113" t="b">
         <v>1</v>
@@ -10443,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="AE113" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.2">
@@ -10451,7 +10448,7 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C114">
         <v>39</v>
@@ -10503,16 +10500,16 @@
         <v>31</v>
       </c>
       <c r="U114" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="W114" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="X114">
         <v>1</v>
       </c>
       <c r="Z114" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA114" t="b">
         <v>1</v>
@@ -10524,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="AE114" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.2">
@@ -10532,7 +10529,7 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C115">
         <v>39</v>
@@ -10584,16 +10581,16 @@
         <v>31</v>
       </c>
       <c r="U115" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="W115" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="X115">
         <v>1</v>
       </c>
       <c r="Z115" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA115" t="b">
         <v>1</v>
@@ -10605,7 +10602,7 @@
         <v>0</v>
       </c>
       <c r="AE115" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.2">
@@ -10613,7 +10610,7 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C116">
         <v>40</v>
@@ -10668,10 +10665,10 @@
         <v>31</v>
       </c>
       <c r="U116" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Z116" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -10683,7 +10680,7 @@
         <v>1</v>
       </c>
       <c r="AE116" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -10691,7 +10688,7 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C117">
         <v>40</v>
@@ -10746,10 +10743,10 @@
         <v>31</v>
       </c>
       <c r="U117" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Z117" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -10761,7 +10758,7 @@
         <v>1</v>
       </c>
       <c r="AE117" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -10769,7 +10766,7 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C118">
         <v>40</v>
@@ -10824,10 +10821,10 @@
         <v>31</v>
       </c>
       <c r="U118" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="Z118" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -10839,22 +10836,22 @@
         <v>1</v>
       </c>
       <c r="AE118" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE119" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE120" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE121" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.2">
@@ -10862,7 +10859,7 @@
         <v>201</v>
       </c>
       <c r="B122" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C122">
         <v>89</v>
@@ -10898,7 +10895,7 @@
         <v>99</v>
       </c>
       <c r="R122" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S122" t="s">
         <v>32</v>
@@ -10916,7 +10913,7 @@
         <v>0</v>
       </c>
       <c r="AE122" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="123" spans="1:31" x14ac:dyDescent="0.2">
@@ -10924,7 +10921,7 @@
         <v>202</v>
       </c>
       <c r="B123" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C123">
         <v>90</v>
@@ -10960,7 +10957,7 @@
         <v>99</v>
       </c>
       <c r="R123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S123" t="s">
         <v>32</v>
@@ -10978,12 +10975,12 @@
         <v>0</v>
       </c>
       <c r="AE123" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE124" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="125" spans="1:31" x14ac:dyDescent="0.2">
@@ -10991,7 +10988,7 @@
         <v>301</v>
       </c>
       <c r="B125" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C125">
         <v>91</v>
@@ -11046,11 +11043,11 @@
         <v>31</v>
       </c>
       <c r="U125" t="s">
+        <v>414</v>
+      </c>
+      <c r="Z125" t="s">
         <v>416</v>
       </c>
-      <c r="Z125" t="s">
-        <v>418</v>
-      </c>
       <c r="AA125" t="b">
         <v>1</v>
       </c>
@@ -11061,7 +11058,7 @@
         <v>1</v>
       </c>
       <c r="AE125" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="126" spans="1:31" x14ac:dyDescent="0.2">
@@ -11069,7 +11066,7 @@
         <v>302</v>
       </c>
       <c r="B126" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C126">
         <v>92</v>
@@ -11115,19 +11112,19 @@
         <v>0</v>
       </c>
       <c r="R126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S126" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="T126" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X126">
         <v>207</v>
       </c>
       <c r="Z126" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AA126" t="b">
         <v>1</v>
@@ -11139,7 +11136,7 @@
         <v>0</v>
       </c>
       <c r="AE126" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="127" spans="1:31" x14ac:dyDescent="0.2">
@@ -11147,7 +11144,7 @@
         <v>303</v>
       </c>
       <c r="B127" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C127">
         <v>93</v>
@@ -11202,10 +11199,10 @@
         <v>31</v>
       </c>
       <c r="U127" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z127" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -11217,12 +11214,12 @@
         <v>0</v>
       </c>
       <c r="AE127" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE128" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="1:31" x14ac:dyDescent="0.2">
@@ -11230,7 +11227,7 @@
         <v>401</v>
       </c>
       <c r="B129" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C129">
         <v>150</v>
@@ -11285,10 +11282,10 @@
         <v>31</v>
       </c>
       <c r="U129" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Z129" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA129" t="b">
         <v>1</v>
@@ -11300,7 +11297,7 @@
         <v>1</v>
       </c>
       <c r="AE129" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="130" spans="1:31" x14ac:dyDescent="0.2">
@@ -11308,7 +11305,7 @@
         <v>402</v>
       </c>
       <c r="B130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C130">
         <v>150</v>
@@ -11363,10 +11360,10 @@
         <v>31</v>
       </c>
       <c r="U130" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Z130" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA130" t="b">
         <v>1</v>
@@ -11378,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="AE130" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="1:31" x14ac:dyDescent="0.2">
@@ -11386,7 +11383,7 @@
         <v>403</v>
       </c>
       <c r="B131" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C131">
         <v>150</v>
@@ -11441,10 +11438,10 @@
         <v>31</v>
       </c>
       <c r="U131" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="Z131" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA131" t="b">
         <v>1</v>
@@ -11456,7 +11453,7 @@
         <v>1</v>
       </c>
       <c r="AE131" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:31" x14ac:dyDescent="0.2">
@@ -11464,7 +11461,7 @@
         <v>404</v>
       </c>
       <c r="B132" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C132">
         <v>151</v>
@@ -11519,10 +11516,10 @@
         <v>31</v>
       </c>
       <c r="U132" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="Z132" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA132" t="b">
         <v>1</v>
@@ -11534,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="AE132" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="133" spans="1:31" x14ac:dyDescent="0.2">
@@ -11542,7 +11539,7 @@
         <v>405</v>
       </c>
       <c r="B133" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C133">
         <v>151</v>
@@ -11597,10 +11594,10 @@
         <v>31</v>
       </c>
       <c r="U133" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z133" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA133" t="b">
         <v>1</v>
@@ -11612,7 +11609,7 @@
         <v>1</v>
       </c>
       <c r="AE133" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="134" spans="1:31" x14ac:dyDescent="0.2">
@@ -11620,7 +11617,7 @@
         <v>406</v>
       </c>
       <c r="B134" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C134">
         <v>151</v>
@@ -11675,10 +11672,10 @@
         <v>31</v>
       </c>
       <c r="U134" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Z134" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA134" t="b">
         <v>1</v>
@@ -11690,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="AE134" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="135" spans="1:31" x14ac:dyDescent="0.2">
@@ -11698,7 +11695,7 @@
         <v>407</v>
       </c>
       <c r="B135" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C135">
         <v>152</v>
@@ -11753,10 +11750,10 @@
         <v>31</v>
       </c>
       <c r="U135" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Z135" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA135" t="b">
         <v>1</v>
@@ -11768,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="AE135" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="136" spans="1:31" x14ac:dyDescent="0.2">
@@ -11776,7 +11773,7 @@
         <v>408</v>
       </c>
       <c r="B136" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C136">
         <v>152</v>
@@ -11831,10 +11828,10 @@
         <v>31</v>
       </c>
       <c r="U136" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z136" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA136" t="b">
         <v>1</v>
@@ -11846,7 +11843,7 @@
         <v>1</v>
       </c>
       <c r="AE136" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="137" spans="1:31" x14ac:dyDescent="0.2">
@@ -11854,7 +11851,7 @@
         <v>409</v>
       </c>
       <c r="B137" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C137">
         <v>152</v>
@@ -11909,10 +11906,10 @@
         <v>31</v>
       </c>
       <c r="U137" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z137" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AA137" t="b">
         <v>1</v>
@@ -11924,377 +11921,377 @@
         <v>1</v>
       </c>
       <c r="AE137" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE138" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="139" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE139" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE140" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE141" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE142" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE143" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="AE144" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE145" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="146" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE146" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE147" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE148" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="149" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE149" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="150" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE150" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="151" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE151" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="152" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE152" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="153" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE153" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE154" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="155" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE155" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="156" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE156" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="157" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE157" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE158" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="159" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE159" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="160" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE160" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="161" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE161" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE162" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="163" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE163" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="164" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE164" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE165" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE166" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="167" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE167" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="168" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE168" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="169" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE169" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE170" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="171" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE171" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE172" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="173" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE173" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="174" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE174" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="175" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE175" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE176" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="177" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE177" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE178" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="179" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE179" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="180" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE180" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE181" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="182" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE182" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="183" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE183" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE184" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="185" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE185" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="186" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE186" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="187" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE187" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE188" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE189" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE190" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE191" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE192" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE193" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE194" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE195" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE196" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE197" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE198" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="199" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE199" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="200" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE200" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="201" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE201" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="202" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE202" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE203" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="204" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE204" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="205" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE205" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="206" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE206" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="207" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE207" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="208" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE208" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="209" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE209" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE210" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
     <row r="211" spans="31:31" x14ac:dyDescent="0.2">
       <c r="AE211" t="s">
-        <v>48</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -12331,66 +12328,66 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" t="s">
         <v>243</v>
       </c>
-      <c r="C1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>245</v>
-      </c>
-      <c r="E1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" t="s">
         <v>246</v>
       </c>
-      <c r="C2" t="s">
-        <v>248</v>
-      </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" t="s">
         <v>244</v>
       </c>
-      <c r="C3" t="s">
-        <v>246</v>
-      </c>
       <c r="D3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -12398,16 +12395,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" t="s">
         <v>147</v>
-      </c>
-      <c r="E8" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -12415,16 +12412,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
         <v>147</v>
-      </c>
-      <c r="E9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -12432,16 +12429,16 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" t="s">
         <v>147</v>
-      </c>
-      <c r="E10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -12449,16 +12446,16 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" t="s">
         <v>151</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -12466,16 +12463,16 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" t="s">
         <v>151</v>
-      </c>
-      <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -12483,16 +12480,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" t="s">
         <v>151</v>
-      </c>
-      <c r="D13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -12500,16 +12497,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14" t="s">
         <v>156</v>
-      </c>
-      <c r="D14" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -12517,16 +12514,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" t="s">
         <v>156</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -12534,16 +12531,16 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" t="s">
         <v>156</v>
-      </c>
-      <c r="D16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -12551,16 +12548,16 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" t="s">
         <v>158</v>
-      </c>
-      <c r="D17" t="s">
-        <v>147</v>
-      </c>
-      <c r="E17" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -12568,10 +12565,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -12579,16 +12576,16 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" t="s">
         <v>160</v>
-      </c>
-      <c r="E19" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -12596,16 +12593,16 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" t="s">
         <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -12613,16 +12610,16 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" t="s">
         <v>147</v>
-      </c>
-      <c r="E21" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -12630,16 +12627,16 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
         <v>147</v>
-      </c>
-      <c r="E22" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -12647,16 +12644,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -12664,16 +12661,16 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C24" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" t="s">
         <v>158</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -12681,16 +12678,16 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" t="s">
         <v>158</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -12698,16 +12695,16 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
         <v>158</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -12715,16 +12712,16 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" t="s">
         <v>164</v>
-      </c>
-      <c r="D27" t="s">
-        <v>163</v>
-      </c>
-      <c r="E27" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -12732,16 +12729,16 @@
         <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" t="s">
         <v>164</v>
-      </c>
-      <c r="D28" t="s">
-        <v>163</v>
-      </c>
-      <c r="E28" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -12749,16 +12746,16 @@
         <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" t="s">
         <v>164</v>
-      </c>
-      <c r="D29" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -12766,16 +12763,16 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" t="s">
         <v>167</v>
-      </c>
-      <c r="D30" t="s">
-        <v>166</v>
-      </c>
-      <c r="E30" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -12783,16 +12780,16 @@
         <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" t="s">
         <v>167</v>
-      </c>
-      <c r="D31" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -12800,16 +12797,16 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
+        <v>166</v>
+      </c>
+      <c r="D32" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
         <v>167</v>
-      </c>
-      <c r="D32" t="s">
-        <v>170</v>
-      </c>
-      <c r="E32" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -12817,16 +12814,16 @@
         <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
         <v>147</v>
-      </c>
-      <c r="E33" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -12834,16 +12831,16 @@
         <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" t="s">
         <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -12851,16 +12848,16 @@
         <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" t="s">
         <v>147</v>
-      </c>
-      <c r="E35" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -12868,16 +12865,16 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" t="s">
         <v>147</v>
-      </c>
-      <c r="E36" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -12885,16 +12882,16 @@
         <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
         <v>147</v>
-      </c>
-      <c r="E37" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -12902,16 +12899,16 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -12919,16 +12916,16 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -12936,16 +12933,16 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -12953,16 +12950,16 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" t="s">
         <v>173</v>
-      </c>
-      <c r="E41" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -12970,16 +12967,16 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
         <v>173</v>
-      </c>
-      <c r="E42" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -12987,16 +12984,16 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
         <v>173</v>
-      </c>
-      <c r="E43" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -13004,16 +13001,16 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D44" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" t="s">
         <v>176</v>
-      </c>
-      <c r="E44" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -13021,16 +13018,16 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D45" t="s">
+        <v>175</v>
+      </c>
+      <c r="E45" t="s">
         <v>176</v>
-      </c>
-      <c r="E45" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -13038,16 +13035,16 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
         <v>176</v>
-      </c>
-      <c r="E46" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -13055,16 +13052,16 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E47" t="s">
         <v>179</v>
-      </c>
-      <c r="E47" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -13072,16 +13069,16 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
         <v>179</v>
-      </c>
-      <c r="E48" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -13089,16 +13086,16 @@
         <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D49" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" t="s">
         <v>179</v>
-      </c>
-      <c r="E49" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -13106,16 +13103,16 @@
         <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" t="s">
         <v>179</v>
-      </c>
-      <c r="E50" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
@@ -13123,16 +13120,16 @@
         <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" t="s">
         <v>179</v>
-      </c>
-      <c r="E51" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -13140,16 +13137,16 @@
         <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" t="s">
         <v>182</v>
-      </c>
-      <c r="E52" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -13157,16 +13154,16 @@
         <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D53" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53" t="s">
         <v>182</v>
-      </c>
-      <c r="E53" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
@@ -13174,16 +13171,16 @@
         <v>47</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D54" t="s">
+        <v>181</v>
+      </c>
+      <c r="E54" t="s">
         <v>182</v>
-      </c>
-      <c r="E54" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -13191,16 +13188,16 @@
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" t="s">
         <v>182</v>
-      </c>
-      <c r="E55" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -13208,16 +13205,16 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" t="s">
         <v>182</v>
-      </c>
-      <c r="E56" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -13225,16 +13222,16 @@
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" t="s">
+        <v>146</v>
+      </c>
+      <c r="E57" t="s">
         <v>158</v>
-      </c>
-      <c r="D57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E57" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -13242,16 +13239,16 @@
         <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" t="s">
+        <v>146</v>
+      </c>
+      <c r="E58" t="s">
         <v>158</v>
-      </c>
-      <c r="D58" t="s">
-        <v>147</v>
-      </c>
-      <c r="E58" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
@@ -13259,16 +13256,16 @@
         <v>52</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
         <v>185</v>
-      </c>
-      <c r="E59" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
@@ -13276,16 +13273,16 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E60" t="s">
         <v>185</v>
-      </c>
-      <c r="E60" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
@@ -13293,16 +13290,16 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D61" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" t="s">
         <v>185</v>
-      </c>
-      <c r="E61" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -13310,16 +13307,16 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D62" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" t="s">
         <v>185</v>
-      </c>
-      <c r="E62" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
@@ -13327,16 +13324,16 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D63" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" t="s">
         <v>185</v>
-      </c>
-      <c r="E63" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -13344,16 +13341,16 @@
         <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D64" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" t="s">
         <v>147</v>
-      </c>
-      <c r="E64" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -13361,16 +13358,16 @@
         <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D65" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" t="s">
         <v>147</v>
-      </c>
-      <c r="E65" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -13378,16 +13375,16 @@
         <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" t="s">
         <v>147</v>
-      </c>
-      <c r="E66" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -13401,7 +13398,7 @@
         <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -13409,7 +13406,7 @@
         <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -13417,7 +13414,7 @@
         <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -13425,7 +13422,7 @@
         <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -13433,7 +13430,7 @@
         <v>84</v>
       </c>
       <c r="B73" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -13441,7 +13438,7 @@
         <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -13449,7 +13446,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -13457,7 +13454,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -13465,7 +13462,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -13473,7 +13470,7 @@
         <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -13481,7 +13478,7 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -13489,7 +13486,7 @@
         <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="81" spans="1:20" x14ac:dyDescent="0.2">
@@ -13497,7 +13494,7 @@
         <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:20" x14ac:dyDescent="0.2">
@@ -13505,7 +13502,7 @@
         <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:20" x14ac:dyDescent="0.2">
@@ -13513,7 +13510,7 @@
         <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:20" x14ac:dyDescent="0.2">
@@ -13521,7 +13518,7 @@
         <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:20" x14ac:dyDescent="0.2">
@@ -13529,7 +13526,7 @@
         <v>96</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:20" x14ac:dyDescent="0.2">
@@ -13537,7 +13534,7 @@
         <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:20" x14ac:dyDescent="0.2">
@@ -13545,7 +13542,7 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:20" x14ac:dyDescent="0.2">
@@ -13553,7 +13550,7 @@
         <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="1:20" x14ac:dyDescent="0.2">
@@ -13561,7 +13558,7 @@
         <v>100</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="1:20" x14ac:dyDescent="0.2">
@@ -13569,7 +13566,7 @@
         <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:20" x14ac:dyDescent="0.2">
@@ -13577,7 +13574,7 @@
         <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:20" x14ac:dyDescent="0.2">
@@ -13585,7 +13582,7 @@
         <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:20" x14ac:dyDescent="0.2">
@@ -13593,13 +13590,13 @@
         <v>104</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D93" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T93" s="1"/>
     </row>
@@ -13608,13 +13605,13 @@
         <v>105</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D94" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E94" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="T94" s="1"/>
     </row>
@@ -13623,13 +13620,13 @@
         <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D95" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E95" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="T95" s="1"/>
     </row>
@@ -13638,13 +13635,13 @@
         <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D96" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="T96" s="1"/>
     </row>
@@ -13653,13 +13650,13 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D97" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E97" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="T97" s="1"/>
     </row>
@@ -13668,13 +13665,13 @@
         <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D98" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="T98" s="1"/>
     </row>
@@ -13683,13 +13680,13 @@
         <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D99" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E99" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="T99" s="1"/>
     </row>
@@ -13698,13 +13695,13 @@
         <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D100" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E100" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="T100" s="1"/>
     </row>
@@ -13713,13 +13710,13 @@
         <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D101" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E101" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T101" s="1"/>
     </row>
@@ -13728,13 +13725,13 @@
         <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D102" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E102" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="T102" s="1"/>
     </row>
@@ -13743,13 +13740,13 @@
         <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E103" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="T103" s="1"/>
     </row>
@@ -13758,13 +13755,13 @@
         <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E104" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="T104" s="1"/>
     </row>
@@ -13773,13 +13770,13 @@
         <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D105" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E105" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="T105" s="1"/>
     </row>
@@ -13788,13 +13785,13 @@
         <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D106" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E106" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="T106" s="1"/>
     </row>
@@ -13803,13 +13800,13 @@
         <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E107" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="T107" s="1"/>
     </row>
@@ -13818,13 +13815,13 @@
         <v>119</v>
       </c>
       <c r="B108" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D108" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E108" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T108" s="1"/>
     </row>
@@ -13833,13 +13830,13 @@
         <v>120</v>
       </c>
       <c r="B109" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D109" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E109" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T109" s="1"/>
     </row>
@@ -13848,13 +13845,13 @@
         <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D110" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E110" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T110" s="1"/>
     </row>
@@ -13863,10 +13860,10 @@
         <v>122</v>
       </c>
       <c r="B111" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D111" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.2">
@@ -13874,10 +13871,10 @@
         <v>123</v>
       </c>
       <c r="B112" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D112" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -13885,10 +13882,10 @@
         <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D113" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -13896,7 +13893,7 @@
         <v>125</v>
       </c>
       <c r="B114" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -13904,7 +13901,7 @@
         <v>126</v>
       </c>
       <c r="B115" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -13912,7 +13909,7 @@
         <v>127</v>
       </c>
       <c r="B116" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -13920,10 +13917,10 @@
         <v>128</v>
       </c>
       <c r="B117" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D117" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -13931,10 +13928,10 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
+        <v>316</v>
+      </c>
+      <c r="D118" t="s">
         <v>318</v>
-      </c>
-      <c r="D118" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -13942,10 +13939,10 @@
         <v>130</v>
       </c>
       <c r="B119" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D119" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -13953,10 +13950,10 @@
         <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D120" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -13964,10 +13961,10 @@
         <v>132</v>
       </c>
       <c r="B121" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D121" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -13975,10 +13972,10 @@
         <v>133</v>
       </c>
       <c r="B122" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D122" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -13986,16 +13983,16 @@
         <v>134</v>
       </c>
       <c r="B123" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C123" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D123" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E123" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -14003,16 +14000,16 @@
         <v>135</v>
       </c>
       <c r="B124" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C124" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D124" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E124" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -14020,16 +14017,16 @@
         <v>136</v>
       </c>
       <c r="B125" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C125" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D125" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E125" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -14037,10 +14034,10 @@
         <v>137</v>
       </c>
       <c r="B126" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D126" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -14048,10 +14045,10 @@
         <v>138</v>
       </c>
       <c r="B127" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D127" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -14059,10 +14056,10 @@
         <v>139</v>
       </c>
       <c r="B128" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D128" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
@@ -14070,13 +14067,13 @@
         <v>140</v>
       </c>
       <c r="B129" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D129" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E129" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
@@ -14084,13 +14081,13 @@
         <v>141</v>
       </c>
       <c r="B130" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D130" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E130" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
@@ -14098,13 +14095,13 @@
         <v>142</v>
       </c>
       <c r="B131" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D131" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E131" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
@@ -14112,16 +14109,16 @@
         <v>143</v>
       </c>
       <c r="B132" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C132" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D132" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E132" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
@@ -14129,16 +14126,16 @@
         <v>144</v>
       </c>
       <c r="B133" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C133" t="s">
+        <v>355</v>
+      </c>
+      <c r="D133" t="s">
         <v>357</v>
       </c>
-      <c r="D133" t="s">
-        <v>359</v>
-      </c>
       <c r="E133" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
@@ -14146,16 +14143,16 @@
         <v>145</v>
       </c>
       <c r="B134" t="s">
+        <v>353</v>
+      </c>
+      <c r="C134" t="s">
         <v>355</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
         <v>357</v>
       </c>
-      <c r="D134" t="s">
-        <v>359</v>
-      </c>
       <c r="E134" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
+++ b/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\project\unity\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\me\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF1EBBF-09EF-4872-80D8-178520BCEDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90162F0-E99D-4F43-8F6E-7E89CC69279E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{85F091D7-8DEA-4479-A83C-808C693C032A}"/>
+    <workbookView xWindow="5472" yWindow="2604" windowWidth="23040" windowHeight="12000" xr2:uid="{85F091D7-8DEA-4479-A83C-808C693C032A}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="462">
   <si>
     <t>名字</t>
   </si>
@@ -1736,6 +1736,18 @@
   </si>
   <si>
     <t>Icon/Skill/Icon_Magic1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹道类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2077,42 +2089,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ211"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AK211"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="26.125" customWidth="1"/>
-    <col min="3" max="3" width="6.375" customWidth="1"/>
-    <col min="4" max="4" width="7.5" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="7" width="6.5" customWidth="1"/>
-    <col min="8" max="8" width="9.75" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="9.75" customWidth="1"/>
-    <col min="11" max="11" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="18.875" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="33.25" customWidth="1"/>
-    <col min="22" max="22" width="44.375" customWidth="1"/>
-    <col min="23" max="23" width="33.25" customWidth="1"/>
-    <col min="24" max="24" width="12.375" customWidth="1"/>
-    <col min="25" max="25" width="11.875" customWidth="1"/>
-    <col min="26" max="26" width="22.625" customWidth="1"/>
-    <col min="27" max="27" width="14.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="15.625" customWidth="1"/>
-    <col min="30" max="30" width="14.25" customWidth="1"/>
-    <col min="31" max="31" width="28.125" customWidth="1"/>
-    <col min="34" max="34" width="9.75" customWidth="1"/>
-    <col min="35" max="35" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="25" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="51.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1"/>
       <c r="B1" t="s">
         <v>0</v>
@@ -2198,8 +2214,11 @@
       <c r="AE1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" ht="15" x14ac:dyDescent="0.2">
+      <c r="AF1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2293,9 +2312,12 @@
       <c r="AE2" t="s">
         <v>3</v>
       </c>
+      <c r="AF2" t="s">
+        <v>460</v>
+      </c>
       <c r="AI2" s="3"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2383,17 +2405,20 @@
       <c r="AE3" t="s">
         <v>5</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AF3" t="s">
+        <v>461</v>
+      </c>
+      <c r="AI3" t="s">
         <v>431</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>434</v>
       </c>
       <c r="AJ3" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AK3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -2470,17 +2495,20 @@
       <c r="AE4" t="s">
         <v>458</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="s">
         <v>432</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AJ4" t="s">
         <v>435</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -2557,17 +2585,20 @@
       <c r="AE5" t="s">
         <v>458</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AF5">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="s">
         <v>433</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
         <v>436</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -2644,14 +2675,17 @@
       <c r="AE6" t="s">
         <v>458</v>
       </c>
-      <c r="AI6" t="s">
+      <c r="AF6">
+        <v>3</v>
+      </c>
+      <c r="AJ6" t="s">
         <v>437</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AK6" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -2728,11 +2762,14 @@
       <c r="AE7" t="s">
         <v>458</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AF7">
+        <v>4</v>
+      </c>
+      <c r="AK7" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -2809,11 +2846,14 @@
       <c r="AE8" t="s">
         <v>458</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AF8">
+        <v>5</v>
+      </c>
+      <c r="AK8" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -2890,11 +2930,14 @@
       <c r="AE9" t="s">
         <v>458</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AK9" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -2968,11 +3011,14 @@
       <c r="AE10" t="s">
         <v>458</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AF10">
+        <v>7</v>
+      </c>
+      <c r="AK10" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
@@ -3046,11 +3092,14 @@
       <c r="AE11" t="s">
         <v>458</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AF11">
+        <v>8</v>
+      </c>
+      <c r="AK11" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9</v>
       </c>
@@ -3124,11 +3173,14 @@
       <c r="AE12" t="s">
         <v>458</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AK12" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
@@ -3202,8 +3254,11 @@
       <c r="AE13" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
@@ -3280,8 +3335,11 @@
       <c r="AE14" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>12</v>
       </c>
@@ -3355,8 +3413,11 @@
       <c r="AE15" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
@@ -3433,8 +3494,11 @@
       <c r="AE16" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -3511,8 +3575,11 @@
       <c r="AE17" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -3589,8 +3656,11 @@
       <c r="AE18" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -3667,8 +3737,11 @@
       <c r="AE19" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -3745,8 +3818,11 @@
       <c r="AE20" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3823,8 +3899,11 @@
       <c r="AE21" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3901,8 +3980,11 @@
       <c r="AE22" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -3985,8 +4067,11 @@
       <c r="AE23" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -4069,8 +4154,11 @@
       <c r="AE24" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -4153,8 +4241,11 @@
       <c r="AE25" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -4231,8 +4322,11 @@
       <c r="AE26" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -4309,8 +4403,11 @@
       <c r="AE27" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -4387,8 +4484,11 @@
       <c r="AE28" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -4465,8 +4565,11 @@
       <c r="AE29" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -4543,8 +4646,11 @@
       <c r="AE30" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4621,8 +4727,11 @@
       <c r="AE31" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -4699,8 +4808,11 @@
       <c r="AE32" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -4777,8 +4889,11 @@
       <c r="AE33" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -4855,8 +4970,11 @@
       <c r="AE34" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -4933,8 +5051,11 @@
       <c r="AE35" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -5011,8 +5132,11 @@
       <c r="AE36" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -5086,8 +5210,11 @@
       <c r="AE37" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -5161,8 +5288,11 @@
       <c r="AE38" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -5236,8 +5366,11 @@
       <c r="AE39" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -5311,8 +5444,11 @@
       <c r="AE40" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -5386,8 +5522,11 @@
       <c r="AE41" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -5461,8 +5600,11 @@
       <c r="AE42" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -5536,8 +5678,11 @@
       <c r="AE43" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -5611,8 +5756,11 @@
       <c r="AE44" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -5686,8 +5834,11 @@
       <c r="AE45" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -5761,8 +5912,11 @@
       <c r="AE46" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -5836,8 +5990,11 @@
       <c r="AE47" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -5911,8 +6068,11 @@
       <c r="AE48" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -5986,8 +6146,11 @@
       <c r="AE49" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -6061,8 +6224,11 @@
       <c r="AE50" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF50">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -6136,8 +6302,11 @@
       <c r="AE51" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -6211,8 +6380,11 @@
       <c r="AE52" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -6286,8 +6458,11 @@
       <c r="AE53" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -6361,8 +6536,11 @@
       <c r="AE54" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -6439,8 +6617,11 @@
       <c r="AE55" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -6517,8 +6698,11 @@
       <c r="AE56" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -6595,8 +6779,11 @@
       <c r="AE57" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -6670,8 +6857,11 @@
       <c r="AE58" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -6745,8 +6935,11 @@
       <c r="AE59" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -6829,8 +7022,11 @@
       <c r="AE60" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -6913,8 +7109,11 @@
       <c r="AE61" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -6997,8 +7196,11 @@
       <c r="AE62" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF62">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AA63" t="b">
         <v>0</v>
       </c>
@@ -7008,8 +7210,11 @@
       <c r="AC63" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF63">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AA64" t="b">
         <v>0</v>
       </c>
@@ -7019,8 +7224,11 @@
       <c r="AC64" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>80</v>
       </c>
@@ -7087,8 +7295,11 @@
       <c r="AE65" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>81</v>
       </c>
@@ -7155,8 +7366,11 @@
       <c r="AE66" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>82</v>
       </c>
@@ -7223,8 +7437,11 @@
       <c r="AE67" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>83</v>
       </c>
@@ -7291,8 +7508,11 @@
       <c r="AE68" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>84</v>
       </c>
@@ -7359,8 +7579,11 @@
       <c r="AE69" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>85</v>
       </c>
@@ -7427,8 +7650,11 @@
       <c r="AE70" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF70">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>86</v>
       </c>
@@ -7495,8 +7721,11 @@
       <c r="AE71" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>87</v>
       </c>
@@ -7563,8 +7792,11 @@
       <c r="AE72" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>88</v>
       </c>
@@ -7631,8 +7863,11 @@
       <c r="AE73" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>89</v>
       </c>
@@ -7699,8 +7934,11 @@
       <c r="AE74" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>90</v>
       </c>
@@ -7767,8 +8005,11 @@
       <c r="AE75" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>91</v>
       </c>
@@ -7835,8 +8076,11 @@
       <c r="AE76" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>92</v>
       </c>
@@ -7903,8 +8147,11 @@
       <c r="AE77" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>93</v>
       </c>
@@ -7971,8 +8218,11 @@
       <c r="AE78" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>94</v>
       </c>
@@ -8039,8 +8289,11 @@
       <c r="AE79" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>95</v>
       </c>
@@ -8107,8 +8360,11 @@
       <c r="AE80" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF80">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>96</v>
       </c>
@@ -8175,8 +8431,11 @@
       <c r="AE81" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF81">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>97</v>
       </c>
@@ -8243,8 +8502,11 @@
       <c r="AE82" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF82">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>98</v>
       </c>
@@ -8311,8 +8573,11 @@
       <c r="AE83" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>99</v>
       </c>
@@ -8379,8 +8644,11 @@
       <c r="AE84" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>100</v>
       </c>
@@ -8447,8 +8715,11 @@
       <c r="AE85" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>101</v>
       </c>
@@ -8515,8 +8786,11 @@
       <c r="AE86" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>102</v>
       </c>
@@ -8583,8 +8857,11 @@
       <c r="AE87" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF87">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>103</v>
       </c>
@@ -8651,8 +8928,11 @@
       <c r="AE88" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="89" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>104</v>
       </c>
@@ -8719,8 +8999,11 @@
       <c r="AE89" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="90" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>105</v>
       </c>
@@ -8787,8 +9070,11 @@
       <c r="AE90" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="91" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF90">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>106</v>
       </c>
@@ -8855,8 +9141,11 @@
       <c r="AE91" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="92" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>107</v>
       </c>
@@ -8923,8 +9212,11 @@
       <c r="AE92" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="93" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF92">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>108</v>
       </c>
@@ -8991,8 +9283,11 @@
       <c r="AE93" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="94" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF93">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>109</v>
       </c>
@@ -9059,8 +9354,11 @@
       <c r="AE94" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="95" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>110</v>
       </c>
@@ -9130,8 +9428,11 @@
       <c r="AE95" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="96" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>111</v>
       </c>
@@ -9201,8 +9502,11 @@
       <c r="AE96" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="97" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>112</v>
       </c>
@@ -9272,8 +9576,11 @@
       <c r="AE97" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="98" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>113</v>
       </c>
@@ -9343,8 +9650,11 @@
       <c r="AE98" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="99" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>114</v>
       </c>
@@ -9414,8 +9724,11 @@
       <c r="AE99" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="100" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>115</v>
       </c>
@@ -9485,8 +9798,11 @@
       <c r="AE100" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="101" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>116</v>
       </c>
@@ -9556,8 +9872,11 @@
       <c r="AE101" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="102" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF101">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>117</v>
       </c>
@@ -9627,8 +9946,11 @@
       <c r="AE102" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="103" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF102">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>118</v>
       </c>
@@ -9698,8 +10020,11 @@
       <c r="AE103" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="104" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF103">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>119</v>
       </c>
@@ -9769,8 +10094,11 @@
       <c r="AE104" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="105" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>120</v>
       </c>
@@ -9840,8 +10168,11 @@
       <c r="AE105" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="106" spans="1:31" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AF105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>121</v>
       </c>
@@ -9911,8 +10242,11 @@
       <c r="AE106" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>122</v>
       </c>
@@ -9986,8 +10320,11 @@
       <c r="AE107" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF107">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>123</v>
       </c>
@@ -10061,8 +10398,11 @@
       <c r="AE108" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>124</v>
       </c>
@@ -10136,8 +10476,11 @@
       <c r="AE109" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>125</v>
       </c>
@@ -10211,8 +10554,11 @@
       <c r="AE110" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF110">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>126</v>
       </c>
@@ -10286,8 +10632,11 @@
       <c r="AE111" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>127</v>
       </c>
@@ -10361,8 +10710,11 @@
       <c r="AE112" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF112">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>128</v>
       </c>
@@ -10442,8 +10794,11 @@
       <c r="AE113" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>129</v>
       </c>
@@ -10523,8 +10878,11 @@
       <c r="AE114" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>130</v>
       </c>
@@ -10604,8 +10962,11 @@
       <c r="AE115" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>131</v>
       </c>
@@ -10682,8 +11043,11 @@
       <c r="AE116" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>132</v>
       </c>
@@ -10760,8 +11124,11 @@
       <c r="AE117" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>133</v>
       </c>
@@ -10838,23 +11205,35 @@
       <c r="AE118" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE119" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE120" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="121" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE121" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>201</v>
       </c>
@@ -10915,8 +11294,11 @@
       <c r="AE122" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF122">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>202</v>
       </c>
@@ -10977,13 +11359,19 @@
       <c r="AE123" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE124" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>301</v>
       </c>
@@ -11060,8 +11448,11 @@
       <c r="AE125" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>302</v>
       </c>
@@ -11138,8 +11529,11 @@
       <c r="AE126" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF126">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>303</v>
       </c>
@@ -11216,13 +11610,19 @@
       <c r="AE127" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF127">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE128" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>401</v>
       </c>
@@ -11299,8 +11699,11 @@
       <c r="AE129" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF129">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>402</v>
       </c>
@@ -11377,8 +11780,11 @@
       <c r="AE130" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF130">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>403</v>
       </c>
@@ -11455,8 +11861,11 @@
       <c r="AE131" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF131">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>404</v>
       </c>
@@ -11533,8 +11942,11 @@
       <c r="AE132" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF132">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>405</v>
       </c>
@@ -11611,8 +12023,11 @@
       <c r="AE133" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF133">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>406</v>
       </c>
@@ -11689,8 +12104,11 @@
       <c r="AE134" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>407</v>
       </c>
@@ -11767,8 +12185,11 @@
       <c r="AE135" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>408</v>
       </c>
@@ -11845,8 +12266,11 @@
       <c r="AE136" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF136">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>409</v>
       </c>
@@ -11923,375 +12347,600 @@
       <c r="AE137" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF137">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE138" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE139" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF139">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE140" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF140">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE141" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="142" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF141">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE142" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF142">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE143" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF143">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="AE144" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="145" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE145" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="146" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF145">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE146" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="147" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE147" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="148" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE148" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="149" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE149" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="150" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE150" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="151" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF150">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE151" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="152" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF151">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE152" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="153" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE153" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="154" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF153">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE154" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="155" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE155" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="156" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE156" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="157" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF156">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE157" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="158" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF157">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE158" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="159" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF158">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE159" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="160" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF159">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE160" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="161" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF160">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE161" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="162" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE162" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="163" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE163" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="164" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF163">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE164" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="165" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF164">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE165" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="166" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF165">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE166" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="167" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF166">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE167" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="168" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF167">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE168" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="169" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF168">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE169" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="170" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF169">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE170" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="171" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF170">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE171" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="172" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF171">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE172" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="173" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF172">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE173" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="174" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF173">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE174" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="175" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF174">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE175" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="176" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE176" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="177" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF176">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE177" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="178" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF177">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE178" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="179" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF178">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE179" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="180" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF179">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE180" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="181" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF180">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE181" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="182" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF181">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE182" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="183" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF182">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE183" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="184" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF183">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE184" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="185" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF184">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE185" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="186" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF185">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE186" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="187" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF186">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE187" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="188" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF187">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE188" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="189" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF188">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE189" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="190" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF189">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE190" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="191" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF190">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE191" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="192" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF191">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE192" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="193" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF192">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE193" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="194" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE194" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="195" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF194">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE195" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="196" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF195">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE196" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="197" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF196">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE197" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="198" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF197">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE198" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="199" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF198">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE199" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="200" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF199">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE200" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="201" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF200">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE201" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="202" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF201">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE202" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="203" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF202">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE203" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="204" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF203">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE204" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="205" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF204">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE205" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="206" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF205">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE206" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="207" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF206">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE207" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="208" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF207">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE208" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="209" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF208">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE209" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="210" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF209">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE210" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="211" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AF210">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="31:32" x14ac:dyDescent="0.25">
       <c r="AE211" t="s">
         <v>458</v>
+      </c>
+      <c r="AF211">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12301,13 +12950,13 @@
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R4:R1048576" xr:uid="{CF3D3C77-80B9-4F45-9AF8-9B23B973C93F}">
-      <formula1>$AH$3:$AH$5</formula1>
+      <formula1>$AI$3:$AI$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S4:S1048576" xr:uid="{0B7AB7D6-D8EC-4BC5-A234-C3DC50E64206}">
-      <formula1>$AJ$3:$AJ$12</formula1>
+      <formula1>$AK$3:$AK$12</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T4:T1048576" xr:uid="{5E209C65-9C8F-4F7D-938D-D0CC136BC8AD}">
-      <formula1>$AI$3:$AI$6</formula1>
+      <formula1>$AJ$3:$AJ$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12318,15 +12967,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B81CEFD-FC1F-4B37-A493-FEAF0C0F4163}">
   <dimension ref="A1:T134"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.125" customWidth="1"/>
-    <col min="3" max="3" width="32.375" customWidth="1"/>
-    <col min="4" max="4" width="41.625" customWidth="1"/>
-    <col min="5" max="5" width="28.25" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>241</v>
       </c>
@@ -12340,7 +12989,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>241</v>
       </c>
@@ -12357,7 +13006,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>242</v>
       </c>
@@ -12371,7 +13020,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>243</v>
       </c>
@@ -12382,7 +13031,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>245</v>
       </c>
@@ -12390,7 +13039,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -12407,7 +13056,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -12424,7 +13073,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -12441,7 +13090,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>4</v>
       </c>
@@ -12458,7 +13107,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>5</v>
       </c>
@@ -12475,7 +13124,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>6</v>
       </c>
@@ -12492,7 +13141,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>7</v>
       </c>
@@ -12509,7 +13158,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>8</v>
       </c>
@@ -12526,7 +13175,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>9</v>
       </c>
@@ -12543,7 +13192,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>10</v>
       </c>
@@ -12560,7 +13209,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>11</v>
       </c>
@@ -12571,7 +13220,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>12</v>
       </c>
@@ -12588,7 +13237,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>13</v>
       </c>
@@ -12605,7 +13254,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>14</v>
       </c>
@@ -12622,7 +13271,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>15</v>
       </c>
@@ -12639,7 +13288,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>16</v>
       </c>
@@ -12656,7 +13305,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>17</v>
       </c>
@@ -12673,7 +13322,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>18</v>
       </c>
@@ -12690,7 +13339,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>19</v>
       </c>
@@ -12707,7 +13356,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>20</v>
       </c>
@@ -12724,7 +13373,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>21</v>
       </c>
@@ -12741,7 +13390,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>22</v>
       </c>
@@ -12758,7 +13407,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>23</v>
       </c>
@@ -12775,7 +13424,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>24</v>
       </c>
@@ -12792,7 +13441,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>25</v>
       </c>
@@ -12809,7 +13458,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>26</v>
       </c>
@@ -12826,7 +13475,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>27</v>
       </c>
@@ -12843,7 +13492,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>28</v>
       </c>
@@ -12860,7 +13509,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>29</v>
       </c>
@@ -12877,7 +13526,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>30</v>
       </c>
@@ -12894,7 +13543,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>31</v>
       </c>
@@ -12911,7 +13560,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>32</v>
       </c>
@@ -12928,7 +13577,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>33</v>
       </c>
@@ -12945,7 +13594,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>34</v>
       </c>
@@ -12962,7 +13611,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35</v>
       </c>
@@ -12979,7 +13628,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>36</v>
       </c>
@@ -12996,7 +13645,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>37</v>
       </c>
@@ -13013,7 +13662,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>38</v>
       </c>
@@ -13030,7 +13679,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>39</v>
       </c>
@@ -13047,7 +13696,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>40</v>
       </c>
@@ -13064,7 +13713,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>41</v>
       </c>
@@ -13081,7 +13730,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>42</v>
       </c>
@@ -13098,7 +13747,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>43</v>
       </c>
@@ -13115,7 +13764,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>44</v>
       </c>
@@ -13132,7 +13781,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>45</v>
       </c>
@@ -13149,7 +13798,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>46</v>
       </c>
@@ -13166,7 +13815,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>47</v>
       </c>
@@ -13183,7 +13832,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>48</v>
       </c>
@@ -13200,7 +13849,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>49</v>
       </c>
@@ -13217,7 +13866,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>50</v>
       </c>
@@ -13234,7 +13883,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>51</v>
       </c>
@@ -13251,7 +13900,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>52</v>
       </c>
@@ -13268,7 +13917,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>53</v>
       </c>
@@ -13285,7 +13934,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>54</v>
       </c>
@@ -13302,7 +13951,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>55</v>
       </c>
@@ -13319,7 +13968,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>56</v>
       </c>
@@ -13336,7 +13985,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>57</v>
       </c>
@@ -13353,7 +14002,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>58</v>
       </c>
@@ -13370,7 +14019,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>59</v>
       </c>
@@ -13387,13 +14036,13 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>80</v>
       </c>
@@ -13401,7 +14050,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>81</v>
       </c>
@@ -13409,7 +14058,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>82</v>
       </c>
@@ -13417,7 +14066,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>83</v>
       </c>
@@ -13425,7 +14074,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>84</v>
       </c>
@@ -13433,7 +14082,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>85</v>
       </c>
@@ -13441,7 +14090,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>86</v>
       </c>
@@ -13449,7 +14098,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>87</v>
       </c>
@@ -13457,7 +14106,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>88</v>
       </c>
@@ -13465,7 +14114,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>89</v>
       </c>
@@ -13473,7 +14122,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>90</v>
       </c>
@@ -13481,7 +14130,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>91</v>
       </c>
@@ -13489,7 +14138,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>92</v>
       </c>
@@ -13497,7 +14146,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>93</v>
       </c>
@@ -13505,7 +14154,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>94</v>
       </c>
@@ -13513,7 +14162,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>95</v>
       </c>
@@ -13521,7 +14170,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>96</v>
       </c>
@@ -13529,7 +14178,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>97</v>
       </c>
@@ -13537,7 +14186,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>98</v>
       </c>
@@ -13545,7 +14194,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>99</v>
       </c>
@@ -13553,7 +14202,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>100</v>
       </c>
@@ -13561,7 +14210,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>101</v>
       </c>
@@ -13569,7 +14218,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>102</v>
       </c>
@@ -13577,7 +14226,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>103</v>
       </c>
@@ -13585,7 +14234,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>104</v>
       </c>
@@ -13600,7 +14249,7 @@
       </c>
       <c r="T93" s="1"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>105</v>
       </c>
@@ -13615,7 +14264,7 @@
       </c>
       <c r="T94" s="1"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>106</v>
       </c>
@@ -13630,7 +14279,7 @@
       </c>
       <c r="T95" s="1"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>107</v>
       </c>
@@ -13645,7 +14294,7 @@
       </c>
       <c r="T96" s="1"/>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>108</v>
       </c>
@@ -13660,7 +14309,7 @@
       </c>
       <c r="T97" s="1"/>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>109</v>
       </c>
@@ -13675,7 +14324,7 @@
       </c>
       <c r="T98" s="1"/>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>110</v>
       </c>
@@ -13690,7 +14339,7 @@
       </c>
       <c r="T99" s="1"/>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>111</v>
       </c>
@@ -13705,7 +14354,7 @@
       </c>
       <c r="T100" s="1"/>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>112</v>
       </c>
@@ -13720,7 +14369,7 @@
       </c>
       <c r="T101" s="1"/>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>113</v>
       </c>
@@ -13735,7 +14384,7 @@
       </c>
       <c r="T102" s="1"/>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>114</v>
       </c>
@@ -13750,7 +14399,7 @@
       </c>
       <c r="T103" s="1"/>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>115</v>
       </c>
@@ -13765,7 +14414,7 @@
       </c>
       <c r="T104" s="1"/>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>116</v>
       </c>
@@ -13780,7 +14429,7 @@
       </c>
       <c r="T105" s="1"/>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>117</v>
       </c>
@@ -13795,7 +14444,7 @@
       </c>
       <c r="T106" s="1"/>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>118</v>
       </c>
@@ -13810,7 +14459,7 @@
       </c>
       <c r="T107" s="1"/>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>119</v>
       </c>
@@ -13825,7 +14474,7 @@
       </c>
       <c r="T108" s="1"/>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>120</v>
       </c>
@@ -13840,7 +14489,7 @@
       </c>
       <c r="T109" s="1"/>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>121</v>
       </c>
@@ -13855,7 +14504,7 @@
       </c>
       <c r="T110" s="1"/>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>122</v>
       </c>
@@ -13866,7 +14515,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>123</v>
       </c>
@@ -13877,7 +14526,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>124</v>
       </c>
@@ -13888,7 +14537,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>125</v>
       </c>
@@ -13896,7 +14545,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>126</v>
       </c>
@@ -13904,7 +14553,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>127</v>
       </c>
@@ -13912,7 +14561,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>128</v>
       </c>
@@ -13923,7 +14572,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>129</v>
       </c>
@@ -13934,7 +14583,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>130</v>
       </c>
@@ -13945,7 +14594,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>131</v>
       </c>
@@ -13956,7 +14605,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>132</v>
       </c>
@@ -13967,7 +14616,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>133</v>
       </c>
@@ -13978,7 +14627,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>134</v>
       </c>
@@ -13995,7 +14644,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>135</v>
       </c>
@@ -14012,7 +14661,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>136</v>
       </c>
@@ -14029,7 +14678,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>137</v>
       </c>
@@ -14040,7 +14689,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>138</v>
       </c>
@@ -14051,7 +14700,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>139</v>
       </c>
@@ -14062,7 +14711,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>140</v>
       </c>
@@ -14076,7 +14725,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>141</v>
       </c>
@@ -14090,7 +14739,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>142</v>
       </c>
@@ -14104,7 +14753,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>143</v>
       </c>
@@ -14121,7 +14770,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>144</v>
       </c>
@@ -14138,7 +14787,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>145</v>
       </c>

--- a/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
+++ b/Assets/asoliddev - Auto Chess/Config/SkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\me\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90162F0-E99D-4F43-8F6E-7E89CC69279E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED058E4E-261F-4AC1-A6A8-DD32AB2167D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5472" yWindow="2604" windowWidth="23040" windowHeight="12000" xr2:uid="{85F091D7-8DEA-4479-A83C-808C693C032A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{85F091D7-8DEA-4479-A83C-808C693C032A}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillData" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="465">
   <si>
     <t>名字</t>
   </si>
@@ -1748,6 +1748,18 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹道移动速度(每秒移动的距离, 或者每秒旋转的角度,或者从发射到到达目标的时间)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2123,6 +2135,7 @@
     <col min="29" max="30" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="23" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="84.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="29.44140625" bestFit="1" customWidth="1"/>
@@ -2217,6 +2230,9 @@
       <c r="AF1" t="s">
         <v>459</v>
       </c>
+      <c r="AG1" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="2" spans="1:37" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2315,6 +2331,9 @@
       <c r="AF2" t="s">
         <v>460</v>
       </c>
+      <c r="AG2" t="s">
+        <v>462</v>
+      </c>
       <c r="AI2" s="3"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
@@ -2408,6 +2427,9 @@
       <c r="AF3" t="s">
         <v>461</v>
       </c>
+      <c r="AG3" t="s">
+        <v>464</v>
+      </c>
       <c r="AI3" t="s">
         <v>431</v>
       </c>
@@ -2498,6 +2520,9 @@
       <c r="AF4">
         <v>1</v>
       </c>
+      <c r="AG4">
+        <v>5</v>
+      </c>
       <c r="AI4" t="s">
         <v>432</v>
       </c>
@@ -2588,6 +2613,9 @@
       <c r="AF5">
         <v>2</v>
       </c>
+      <c r="AG5">
+        <v>5</v>
+      </c>
       <c r="AI5" t="s">
         <v>433</v>
       </c>
@@ -2678,6 +2706,9 @@
       <c r="AF6">
         <v>3</v>
       </c>
+      <c r="AG6">
+        <v>5</v>
+      </c>
       <c r="AJ6" t="s">
         <v>437</v>
       </c>
@@ -2765,6 +2796,9 @@
       <c r="AF7">
         <v>4</v>
       </c>
+      <c r="AG7">
+        <v>5</v>
+      </c>
       <c r="AK7" t="s">
         <v>441</v>
       </c>
@@ -2849,6 +2883,9 @@
       <c r="AF8">
         <v>5</v>
       </c>
+      <c r="AG8">
+        <v>5</v>
+      </c>
       <c r="AK8" t="s">
         <v>442</v>
       </c>
@@ -2933,6 +2970,9 @@
       <c r="AF9">
         <v>6</v>
       </c>
+      <c r="AG9">
+        <v>5</v>
+      </c>
       <c r="AK9" t="s">
         <v>443</v>
       </c>
@@ -3014,6 +3054,9 @@
       <c r="AF10">
         <v>7</v>
       </c>
+      <c r="AG10">
+        <v>5</v>
+      </c>
       <c r="AK10" t="s">
         <v>444</v>
       </c>
@@ -3095,6 +3138,9 @@
       <c r="AF11">
         <v>8</v>
       </c>
+      <c r="AG11">
+        <v>5</v>
+      </c>
       <c r="AK11" t="s">
         <v>446</v>
       </c>
@@ -3176,6 +3222,9 @@
       <c r="AF12">
         <v>9</v>
       </c>
+      <c r="AG12">
+        <v>5</v>
+      </c>
       <c r="AK12" t="s">
         <v>445</v>
       </c>
@@ -3257,6 +3306,9 @@
       <c r="AF13">
         <v>10</v>
       </c>
+      <c r="AG13">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -3338,6 +3390,9 @@
       <c r="AF14">
         <v>1</v>
       </c>
+      <c r="AG14">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -3416,6 +3471,9 @@
       <c r="AF15">
         <v>2</v>
       </c>
+      <c r="AG15">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -3497,8 +3555,11 @@
       <c r="AF16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
@@ -3578,8 +3639,11 @@
       <c r="AF17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
@@ -3659,8 +3723,11 @@
       <c r="AF18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>16</v>
       </c>
@@ -3740,8 +3807,11 @@
       <c r="AF19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
@@ -3821,8 +3891,11 @@
       <c r="AF20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
@@ -3902,8 +3975,11 @@
       <c r="AF21">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>19</v>
       </c>
@@ -3983,8 +4059,11 @@
       <c r="AF22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
@@ -4070,8 +4149,11 @@
       <c r="AF23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>21</v>
       </c>
@@ -4157,8 +4239,11 @@
       <c r="AF24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:32" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>22</v>
       </c>
@@ -4244,8 +4329,11 @@
       <c r="AF25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>23</v>
       </c>
@@ -4325,8 +4413,11 @@
       <c r="AF26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>24</v>
       </c>
@@ -4406,8 +4497,11 @@
       <c r="AF27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>25</v>
       </c>
@@ -4487,8 +4581,11 @@
       <c r="AF28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>26</v>
       </c>
@@ -4568,8 +4665,11 @@
       <c r="AF29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>27</v>
       </c>
@@ -4649,8 +4749,11 @@
       <c r="AF30">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
@@ -4730,8 +4833,11 @@
       <c r="AF31">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>29</v>
       </c>
@@ -4811,8 +4917,11 @@
       <c r="AF32">
         <v>9</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -4892,8 +5001,11 @@
       <c r="AF33">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -4973,8 +5085,11 @@
       <c r="AF34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -5054,8 +5169,11 @@
       <c r="AF35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -5135,8 +5253,11 @@
       <c r="AF36">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>34</v>
       </c>
@@ -5213,8 +5334,11 @@
       <c r="AF37">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -5291,8 +5415,11 @@
       <c r="AF38">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -5369,8 +5496,11 @@
       <c r="AF39">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -5447,8 +5577,11 @@
       <c r="AF40">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -5525,8 +5658,11 @@
       <c r="AF41">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -5603,8 +5739,11 @@
       <c r="AF42">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -5681,8 +5820,11 @@
       <c r="AF43">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>41</v>
       </c>
@@ -5759,8 +5901,11 @@
       <c r="AF44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>42</v>
       </c>
@@ -5837,8 +5982,11 @@
       <c r="AF45">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>43</v>
       </c>
@@ -5915,8 +6063,11 @@
       <c r="AF46">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>44</v>
       </c>
@@ -5993,8 +6144,11 @@
       <c r="AF47">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45</v>
       </c>
@@ -6071,8 +6225,11 @@
       <c r="AF48">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>46</v>
       </c>
@@ -6149,8 +6306,11 @@
       <c r="AF49">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>47</v>
       </c>
@@ -6227,8 +6387,11 @@
       <c r="AF50">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>48</v>
       </c>
@@ -6305,8 +6468,11 @@
       <c r="AF51">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>49</v>
       </c>
@@ -6383,8 +6549,11 @@
       <c r="AF52">
         <v>9</v>
       </c>
-    </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>50</v>
       </c>
@@ -6461,8 +6630,11 @@
       <c r="AF53">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>51</v>
       </c>
@@ -6539,8 +6711,11 @@
       <c r="AF54">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>52</v>
       </c>
@@ -6620,8 +6795,11 @@
       <c r="AF55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>53</v>
       </c>
@@ -6701,8 +6879,11 @@
       <c r="AF56">
         <v>3</v>
       </c>
-    </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>54</v>
       </c>
@@ -6782,8 +6963,11 @@
       <c r="AF57">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>55</v>
       </c>
@@ -6860,8 +7044,11 @@
       <c r="AF58">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>56</v>
       </c>
@@ -6938,8 +7125,11 @@
       <c r="AF59">
         <v>6</v>
       </c>
-    </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>57</v>
       </c>
@@ -7025,8 +7215,11 @@
       <c r="AF60">
         <v>7</v>
       </c>
-    </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>58</v>
       </c>
@@ -7112,8 +7305,11 @@
       <c r="AF61">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>59</v>
       </c>
@@ -7199,8 +7395,11 @@
       <c r="AF62">
         <v>9</v>
       </c>
-    </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AA63" t="b">
         <v>0</v>
       </c>
@@ -7213,8 +7412,11 @@
       <c r="AF63">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AA64" t="b">
         <v>0</v>
       </c>
@@ -7227,8 +7429,11 @@
       <c r="AF64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>80</v>
       </c>
@@ -7298,8 +7503,11 @@
       <c r="AF65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>81</v>
       </c>
@@ -7369,8 +7577,11 @@
       <c r="AF66">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>82</v>
       </c>
@@ -7440,8 +7651,11 @@
       <c r="AF67">
         <v>4</v>
       </c>
-    </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>83</v>
       </c>
@@ -7511,8 +7725,11 @@
       <c r="AF68">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>84</v>
       </c>
@@ -7582,8 +7799,11 @@
       <c r="AF69">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>85</v>
       </c>
@@ -7653,8 +7873,11 @@
       <c r="AF70">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>86</v>
       </c>
@@ -7724,8 +7947,11 @@
       <c r="AF71">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>87</v>
       </c>
@@ -7795,8 +8021,11 @@
       <c r="AF72">
         <v>9</v>
       </c>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>88</v>
       </c>
@@ -7866,8 +8095,11 @@
       <c r="AF73">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>89</v>
       </c>
@@ -7937,8 +8169,11 @@
       <c r="AF74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>90</v>
       </c>
@@ -8008,8 +8243,11 @@
       <c r="AF75">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>91</v>
       </c>
@@ -8079,8 +8317,11 @@
       <c r="AF76">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>92</v>
       </c>
@@ -8150,8 +8391,11 @@
       <c r="AF77">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>93</v>
       </c>
@@ -8221,8 +8465,11 @@
       <c r="AF78">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>94</v>
       </c>
@@ -8292,8 +8539,11 @@
       <c r="AF79">
         <v>6</v>
       </c>
-    </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>95</v>
       </c>
@@ -8363,8 +8613,11 @@
       <c r="AF80">
         <v>7</v>
       </c>
-    </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>96</v>
       </c>
@@ -8434,8 +8687,11 @@
       <c r="AF81">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>97</v>
       </c>
@@ -8505,8 +8761,11 @@
       <c r="AF82">
         <v>9</v>
       </c>
-    </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>98</v>
       </c>
@@ -8576,8 +8835,11 @@
       <c r="AF83">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>99</v>
       </c>
@@ -8647,8 +8909,11 @@
       <c r="AF84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>100</v>
       </c>
@@ -8718,8 +8983,11 @@
       <c r="AF85">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>101</v>
       </c>
@@ -8789,8 +9057,11 @@
       <c r="AF86">
         <v>3</v>
       </c>
-    </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>102</v>
       </c>
@@ -8860,8 +9131,11 @@
       <c r="AF87">
         <v>4</v>
       </c>
-    </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>103</v>
       </c>
@@ -8931,8 +9205,11 @@
       <c r="AF88">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>104</v>
       </c>
@@ -9002,8 +9279,11 @@
       <c r="AF89">
         <v>6</v>
       </c>
-    </row>
-    <row r="90" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>105</v>
       </c>
@@ -9073,8 +9353,11 @@
       <c r="AF90">
         <v>7</v>
       </c>
-    </row>
-    <row r="91" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>106</v>
       </c>
@@ -9144,8 +9427,11 @@
       <c r="AF91">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>107</v>
       </c>
@@ -9215,8 +9501,11 @@
       <c r="AF92">
         <v>9</v>
       </c>
-    </row>
-    <row r="93" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>108</v>
       </c>
@@ -9286,8 +9575,11 @@
       <c r="AF93">
         <v>10</v>
       </c>
-    </row>
-    <row r="94" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>109</v>
       </c>
@@ -9357,8 +9649,11 @@
       <c r="AF94">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>110</v>
       </c>
@@ -9431,8 +9726,11 @@
       <c r="AF95">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>111</v>
       </c>
@@ -9505,8 +9803,11 @@
       <c r="AF96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>112</v>
       </c>
@@ -9579,8 +9880,11 @@
       <c r="AF97">
         <v>4</v>
       </c>
-    </row>
-    <row r="98" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>113</v>
       </c>
@@ -9653,8 +9957,11 @@
       <c r="AF98">
         <v>5</v>
       </c>
-    </row>
-    <row r="99" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>114</v>
       </c>
@@ -9727,8 +10034,11 @@
       <c r="AF99">
         <v>6</v>
       </c>
-    </row>
-    <row r="100" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>115</v>
       </c>
@@ -9801,8 +10111,11 @@
       <c r="AF100">
         <v>7</v>
       </c>
-    </row>
-    <row r="101" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="AG100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>116</v>
       </c>
@@ -9875,8 +10188,11 @@
       <c r="AF101">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="AG101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>117</v>
       </c>
@@ -9949,8 +10265,11 @@
       <c r="AF102">
         <v>9</v>
       </c>
-    </row>
-    <row r="103" spans="1:32" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="AG102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>118</v>
       </c>
@@ -10023,8 +10342,11 @@
       <c r="AF103">
         <v>10</v>
       </c>
-    </row>
-    <row r="104" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>119</v>
       </c>
@@ -10097,8 +10419,11 @@
       <c r="AF104">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>120</v>
       </c>
@@ -10171,8 +10496,11 @@
       <c r="AF105">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:32" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="AG105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:33" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>121</v>
       </c>
@@ -10245,8 +10573,11 @@
       <c r="AF106">
         <v>3</v>
       </c>
-    </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>122</v>
       </c>
@@ -10323,8 +10654,11 @@
       <c r="AF107">
         <v>4</v>
       </c>
-    </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>123</v>
       </c>
@@ -10401,8 +10735,11 @@
       <c r="AF108">
         <v>5</v>
       </c>
-    </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>124</v>
       </c>
@@ -10479,8 +10816,11 @@
       <c r="AF109">
         <v>6</v>
       </c>
-    </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>125</v>
       </c>
@@ -10557,8 +10897,11 @@
       <c r="AF110">
         <v>7</v>
       </c>
-    </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>126</v>
       </c>
@@ -10635,8 +10978,11 @@
       <c r="AF111">
         <v>8</v>
       </c>
-    </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>127</v>
       </c>
@@ -10713,8 +11059,11 @@
       <c r="AF112">
         <v>9</v>
       </c>
-    </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>128</v>
       </c>
@@ -10797,8 +11146,11 @@
       <c r="AF113">
         <v>10</v>
       </c>
-    </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>129</v>
       </c>
@@ -10881,8 +11233,11 @@
       <c r="AF114">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>130</v>
       </c>
@@ -10965,8 +11320,11 @@
       <c r="AF115">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG115">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>131</v>
       </c>
@@ -11046,8 +11404,11 @@
       <c r="AF116">
         <v>3</v>
       </c>
-    </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>132</v>
       </c>
@@ -11127,8 +11488,11 @@
       <c r="AF117">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>133</v>
       </c>
@@ -11208,32 +11572,44 @@
       <c r="AF118">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE119" t="s">
         <v>458</v>
       </c>
       <c r="AF119">
         <v>6</v>
       </c>
-    </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE120" t="s">
         <v>458</v>
       </c>
       <c r="AF120">
         <v>7</v>
       </c>
-    </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE121" t="s">
         <v>458</v>
       </c>
       <c r="AF121">
         <v>8</v>
       </c>
-    </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>201</v>
       </c>
@@ -11297,8 +11673,11 @@
       <c r="AF122">
         <v>9</v>
       </c>
-    </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>202</v>
       </c>
@@ -11362,16 +11741,22 @@
       <c r="AF123">
         <v>10</v>
       </c>
-    </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG123">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE124" t="s">
         <v>458</v>
       </c>
       <c r="AF124">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG124">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>301</v>
       </c>
@@ -11451,8 +11836,11 @@
       <c r="AF125">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>302</v>
       </c>
@@ -11532,8 +11920,11 @@
       <c r="AF126">
         <v>3</v>
       </c>
-    </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>303</v>
       </c>
@@ -11613,16 +12004,22 @@
       <c r="AF127">
         <v>4</v>
       </c>
-    </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE128" t="s">
         <v>458</v>
       </c>
       <c r="AF128">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>401</v>
       </c>
@@ -11702,8 +12099,11 @@
       <c r="AF129">
         <v>6</v>
       </c>
-    </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG129">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>402</v>
       </c>
@@ -11783,8 +12183,11 @@
       <c r="AF130">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>403</v>
       </c>
@@ -11864,8 +12267,11 @@
       <c r="AF131">
         <v>8</v>
       </c>
-    </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG131">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>404</v>
       </c>
@@ -11945,8 +12351,11 @@
       <c r="AF132">
         <v>9</v>
       </c>
-    </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG132">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>405</v>
       </c>
@@ -12026,8 +12435,11 @@
       <c r="AF133">
         <v>10</v>
       </c>
-    </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>406</v>
       </c>
@@ -12107,8 +12519,11 @@
       <c r="AF134">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG134">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>407</v>
       </c>
@@ -12188,8 +12603,11 @@
       <c r="AF135">
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG135">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>408</v>
       </c>
@@ -12269,8 +12687,11 @@
       <c r="AF136">
         <v>3</v>
       </c>
-    </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG136">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>409</v>
       </c>
@@ -12350,597 +12771,822 @@
       <c r="AF137">
         <v>4</v>
       </c>
-    </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE138" t="s">
         <v>458</v>
       </c>
       <c r="AF138">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE139" t="s">
         <v>458</v>
       </c>
       <c r="AF139">
         <v>6</v>
       </c>
-    </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE140" t="s">
         <v>458</v>
       </c>
       <c r="AF140">
         <v>7</v>
       </c>
-    </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE141" t="s">
         <v>458</v>
       </c>
       <c r="AF141">
         <v>8</v>
       </c>
-    </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE142" t="s">
         <v>458</v>
       </c>
       <c r="AF142">
         <v>9</v>
       </c>
-    </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE143" t="s">
         <v>458</v>
       </c>
       <c r="AF143">
         <v>10</v>
       </c>
-    </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AE144" t="s">
         <v>458</v>
       </c>
       <c r="AF144">
         <v>4</v>
       </c>
-    </row>
-    <row r="145" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG144">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE145" t="s">
         <v>458</v>
       </c>
       <c r="AF145">
         <v>4</v>
       </c>
-    </row>
-    <row r="146" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE146" t="s">
         <v>458</v>
       </c>
       <c r="AF146">
         <v>4</v>
       </c>
-    </row>
-    <row r="147" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE147" t="s">
         <v>458</v>
       </c>
       <c r="AF147">
         <v>4</v>
       </c>
-    </row>
-    <row r="148" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE148" t="s">
         <v>458</v>
       </c>
       <c r="AF148">
         <v>4</v>
       </c>
-    </row>
-    <row r="149" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG148">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE149" t="s">
         <v>458</v>
       </c>
       <c r="AF149">
         <v>4</v>
       </c>
-    </row>
-    <row r="150" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE150" t="s">
         <v>458</v>
       </c>
       <c r="AF150">
         <v>4</v>
       </c>
-    </row>
-    <row r="151" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE151" t="s">
         <v>458</v>
       </c>
       <c r="AF151">
         <v>4</v>
       </c>
-    </row>
-    <row r="152" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE152" t="s">
         <v>458</v>
       </c>
       <c r="AF152">
         <v>4</v>
       </c>
-    </row>
-    <row r="153" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE153" t="s">
         <v>458</v>
       </c>
       <c r="AF153">
         <v>4</v>
       </c>
-    </row>
-    <row r="154" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE154" t="s">
         <v>458</v>
       </c>
       <c r="AF154">
         <v>4</v>
       </c>
-    </row>
-    <row r="155" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE155" t="s">
         <v>458</v>
       </c>
       <c r="AF155">
         <v>4</v>
       </c>
-    </row>
-    <row r="156" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE156" t="s">
         <v>458</v>
       </c>
       <c r="AF156">
         <v>4</v>
       </c>
-    </row>
-    <row r="157" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE157" t="s">
         <v>458</v>
       </c>
       <c r="AF157">
         <v>4</v>
       </c>
-    </row>
-    <row r="158" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE158" t="s">
         <v>458</v>
       </c>
       <c r="AF158">
         <v>4</v>
       </c>
-    </row>
-    <row r="159" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE159" t="s">
         <v>458</v>
       </c>
       <c r="AF159">
         <v>4</v>
       </c>
-    </row>
-    <row r="160" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE160" t="s">
         <v>458</v>
       </c>
       <c r="AF160">
         <v>4</v>
       </c>
-    </row>
-    <row r="161" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE161" t="s">
         <v>458</v>
       </c>
       <c r="AF161">
         <v>4</v>
       </c>
-    </row>
-    <row r="162" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE162" t="s">
         <v>458</v>
       </c>
       <c r="AF162">
         <v>4</v>
       </c>
-    </row>
-    <row r="163" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE163" t="s">
         <v>458</v>
       </c>
       <c r="AF163">
         <v>4</v>
       </c>
-    </row>
-    <row r="164" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE164" t="s">
         <v>458</v>
       </c>
       <c r="AF164">
         <v>4</v>
       </c>
-    </row>
-    <row r="165" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE165" t="s">
         <v>458</v>
       </c>
       <c r="AF165">
         <v>4</v>
       </c>
-    </row>
-    <row r="166" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE166" t="s">
         <v>458</v>
       </c>
       <c r="AF166">
         <v>4</v>
       </c>
-    </row>
-    <row r="167" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE167" t="s">
         <v>458</v>
       </c>
       <c r="AF167">
         <v>4</v>
       </c>
-    </row>
-    <row r="168" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE168" t="s">
         <v>458</v>
       </c>
       <c r="AF168">
         <v>4</v>
       </c>
-    </row>
-    <row r="169" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE169" t="s">
         <v>458</v>
       </c>
       <c r="AF169">
         <v>4</v>
       </c>
-    </row>
-    <row r="170" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE170" t="s">
         <v>458</v>
       </c>
       <c r="AF170">
         <v>4</v>
       </c>
-    </row>
-    <row r="171" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE171" t="s">
         <v>458</v>
       </c>
       <c r="AF171">
         <v>4</v>
       </c>
-    </row>
-    <row r="172" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG171">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE172" t="s">
         <v>458</v>
       </c>
       <c r="AF172">
         <v>4</v>
       </c>
-    </row>
-    <row r="173" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE173" t="s">
         <v>458</v>
       </c>
       <c r="AF173">
         <v>4</v>
       </c>
-    </row>
-    <row r="174" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG173">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE174" t="s">
         <v>458</v>
       </c>
       <c r="AF174">
         <v>4</v>
       </c>
-    </row>
-    <row r="175" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE175" t="s">
         <v>458</v>
       </c>
       <c r="AF175">
         <v>4</v>
       </c>
-    </row>
-    <row r="176" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE176" t="s">
         <v>458</v>
       </c>
       <c r="AF176">
         <v>4</v>
       </c>
-    </row>
-    <row r="177" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE177" t="s">
         <v>458</v>
       </c>
       <c r="AF177">
         <v>4</v>
       </c>
-    </row>
-    <row r="178" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE178" t="s">
         <v>458</v>
       </c>
       <c r="AF178">
         <v>4</v>
       </c>
-    </row>
-    <row r="179" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG178">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE179" t="s">
         <v>458</v>
       </c>
       <c r="AF179">
         <v>4</v>
       </c>
-    </row>
-    <row r="180" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE180" t="s">
         <v>458</v>
       </c>
       <c r="AF180">
         <v>4</v>
       </c>
-    </row>
-    <row r="181" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE181" t="s">
         <v>458</v>
       </c>
       <c r="AF181">
         <v>4</v>
       </c>
-    </row>
-    <row r="182" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE182" t="s">
         <v>458</v>
       </c>
       <c r="AF182">
         <v>4</v>
       </c>
-    </row>
-    <row r="183" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE183" t="s">
         <v>458</v>
       </c>
       <c r="AF183">
         <v>4</v>
       </c>
-    </row>
-    <row r="184" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE184" t="s">
         <v>458</v>
       </c>
       <c r="AF184">
         <v>4</v>
       </c>
-    </row>
-    <row r="185" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE185" t="s">
         <v>458</v>
       </c>
       <c r="AF185">
         <v>4</v>
       </c>
-    </row>
-    <row r="186" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG185">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE186" t="s">
         <v>458</v>
       </c>
       <c r="AF186">
         <v>4</v>
       </c>
-    </row>
-    <row r="187" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE187" t="s">
         <v>458</v>
       </c>
       <c r="AF187">
         <v>4</v>
       </c>
-    </row>
-    <row r="188" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE188" t="s">
         <v>458</v>
       </c>
       <c r="AF188">
         <v>4</v>
       </c>
-    </row>
-    <row r="189" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE189" t="s">
         <v>458</v>
       </c>
       <c r="AF189">
         <v>4</v>
       </c>
-    </row>
-    <row r="190" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE190" t="s">
         <v>458</v>
       </c>
       <c r="AF190">
         <v>4</v>
       </c>
-    </row>
-    <row r="191" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE191" t="s">
         <v>458</v>
       </c>
       <c r="AF191">
         <v>4</v>
       </c>
-    </row>
-    <row r="192" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE192" t="s">
         <v>458</v>
       </c>
       <c r="AF192">
         <v>4</v>
       </c>
-    </row>
-    <row r="193" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG192">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE193" t="s">
         <v>458</v>
       </c>
       <c r="AF193">
         <v>4</v>
       </c>
-    </row>
-    <row r="194" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE194" t="s">
         <v>458</v>
       </c>
       <c r="AF194">
         <v>4</v>
       </c>
-    </row>
-    <row r="195" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG194">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE195" t="s">
         <v>458</v>
       </c>
       <c r="AF195">
         <v>4</v>
       </c>
-    </row>
-    <row r="196" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE196" t="s">
         <v>458</v>
       </c>
       <c r="AF196">
         <v>4</v>
       </c>
-    </row>
-    <row r="197" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG196">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE197" t="s">
         <v>458</v>
       </c>
       <c r="AF197">
         <v>4</v>
       </c>
-    </row>
-    <row r="198" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE198" t="s">
         <v>458</v>
       </c>
       <c r="AF198">
         <v>4</v>
       </c>
-    </row>
-    <row r="199" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG198">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE199" t="s">
         <v>458</v>
       </c>
       <c r="AF199">
         <v>4</v>
       </c>
-    </row>
-    <row r="200" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG199">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE200" t="s">
         <v>458</v>
       </c>
       <c r="AF200">
         <v>4</v>
       </c>
-    </row>
-    <row r="201" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE201" t="s">
         <v>458</v>
       </c>
       <c r="AF201">
         <v>4</v>
       </c>
-    </row>
-    <row r="202" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE202" t="s">
         <v>458</v>
       </c>
       <c r="AF202">
         <v>4</v>
       </c>
-    </row>
-    <row r="203" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE203" t="s">
         <v>458</v>
       </c>
       <c r="AF203">
         <v>4</v>
       </c>
-    </row>
-    <row r="204" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG203">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE204" t="s">
         <v>458</v>
       </c>
       <c r="AF204">
         <v>4</v>
       </c>
-    </row>
-    <row r="205" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE205" t="s">
         <v>458</v>
       </c>
       <c r="AF205">
         <v>4</v>
       </c>
-    </row>
-    <row r="206" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE206" t="s">
         <v>458</v>
       </c>
       <c r="AF206">
         <v>4</v>
       </c>
-    </row>
-    <row r="207" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE207" t="s">
         <v>458</v>
       </c>
       <c r="AF207">
         <v>4</v>
       </c>
-    </row>
-    <row r="208" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG207">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE208" t="s">
         <v>458</v>
       </c>
       <c r="AF208">
         <v>4</v>
       </c>
-    </row>
-    <row r="209" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG208">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE209" t="s">
         <v>458</v>
       </c>
       <c r="AF209">
         <v>4</v>
       </c>
-    </row>
-    <row r="210" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE210" t="s">
         <v>458</v>
       </c>
       <c r="AF210">
         <v>4</v>
       </c>
-    </row>
-    <row r="211" spans="31:32" x14ac:dyDescent="0.25">
+      <c r="AG210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="31:33" x14ac:dyDescent="0.25">
       <c r="AE211" t="s">
         <v>458</v>
       </c>
       <c r="AF211">
         <v>4</v>
+      </c>
+      <c r="AG211">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
